--- a/seo-texts/frog/acceptor-top100.xlsx
+++ b/seo-texts/frog/acceptor-top100.xlsx
@@ -429,29 +429,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:Y101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
     <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="66" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,7 +522,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>G живых пок</t>
+          <t>G жив.пок</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -532,7 +537,7 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Y живых пок</t>
+          <t>Y жив.пок</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -547,10 +552,35 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Value БЕЗ бренд-буста</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Буст</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Метрика: визиты/мес</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Метрика: заявки/мес</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Конв. %</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Топ-запросы (живые)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Пометки</t>
         </is>
@@ -623,12 +653,27 @@
       <c r="R2" s="2" t="n">
         <v>203.2</v>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="n">
+        <v>203.2</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>«компрессор» G10.3 (300п); «купить компрессор» G11.5 (178п); «компрессор купить» G17.9 (109п)</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>агент: качать (3 сс.)</t>
         </is>
@@ -697,12 +742,21 @@
       <c r="R3" t="n">
         <v>122.8</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
         <is>
           <t>«компрессор винтовой» G7.8 (228п); «винтовой компрессор» G6.8 (185п); «винтовые компрессоры профессиональный» G9.2 (77п)</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>агент: качать (3 сс.)</t>
         </is>
@@ -771,12 +825,21 @@
       <c r="R4" t="n">
         <v>102.1</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
         <is>
           <t>«кислородная станция» G8.0 (237п); «кислородная станция купить» G11.0 (91п); «кислородная установка купить» G7.8 (88п)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -845,12 +908,21 @@
       <c r="R5" t="n">
         <v>99.7</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
         <is>
           <t>«адсорбционный осушитель сжатого воздуха» G8.6 (109п); «осушитель сжатого воздуха» G12.7 (92п); «осушитель сжатого воздуха адсорбционного типа» G8.5 (87п)</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -917,12 +989,21 @@
       <c r="R6" t="n">
         <v>90.8</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
         <is>
           <t>«безмасляный воздушный компрессор купить» G8.9 (129п); «безмасляные компрессоры» G9.5 (92п); «безмасляные воздушные компрессоры» G6.7 (43п)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -991,12 +1072,21 @@
       <c r="R7" t="n">
         <v>76.8</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
         <is>
           <t>«азотная станция» G13.5 (76п); «азотные компрессорные станции» G11.0 (71п); «установка азота» G9.1 (69п)</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -1065,12 +1155,25 @@
       <c r="R8" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
         <is>
           <t>«компрессор 200 бар» G5.1 (56п); «компрессор 200 атмосфер» G7.2 (49п); «компрессор 200 атм» G7.1 (33п)</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -1139,12 +1242,21 @@
       <c r="R9" t="n">
         <v>58.9</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
         <is>
           <t>«дизель компрессор» Я10.1 (49п); «дизельный передвижной компрессор promcomtech.ru/catalog/dizelnye-kompressory/peredvizhnye/» Я7.1 (42п); «компрессор высокого давления дизельный» Я6.7 (40п)</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -1217,12 +1329,27 @@
       <c r="R10" s="3" t="n">
         <v>47.2</v>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S10" s="3" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>«ремонт и обслуживание компрессоров» G10.9 (170п); «техническое обслуживание компрессоров теплообменников» Я5.0 (155п); «обслуживание винтовых компрессоров» G16.0 (89п)</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -1285,12 +1412,21 @@
       <c r="R11" t="n">
         <v>42.9</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
         <is>
           <t>«генератор азота цена» G18.2 (79п); «генератор азота» G14.1 (62п); «адсорбционный генератор азота» G7.6 (56п)</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -1357,12 +1493,21 @@
       <c r="R12" s="2" t="n">
         <v>39.7</v>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>«компрессор» Я12.1 (29п); «центробежный компрессор» Я11.7 (18п); «осушитель воздуха для компрессора» Я20.0 (10п)</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.); ПИЛОТ</t>
         </is>
@@ -1431,12 +1576,27 @@
       <c r="R13" t="n">
         <v>39.5</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>«винтовой компрессор» G15.0 (458п); «стоимость винтового компрессора» G10.7 (164п); «компрессор промышленный винтовой» G15.7 (116п)</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>агент: качать (3 сс.); ПИЛОТ</t>
         </is>
@@ -1505,12 +1665,21 @@
       <c r="R14" t="n">
         <v>36.7</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
         <is>
           <t>«рефрижераторный осушитель воздуха» G6.4 (164п); «осушитель рефрижераторного типа» G5.8 (152п); «осушитель сжатого воздуха рефрижераторного типа» G5.5 (99п)</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>агент: качать (2 сс.)</t>
         </is>
@@ -1575,12 +1744,21 @@
       <c r="R15" t="n">
         <v>31.8</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S15" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
         <is>
           <t>«модульные компрессорные станции» G6.4 (156п); «модульная компрессорная станция мкс» G8.3 (61п); «компрессорная» G8.3 (45п)</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1641,12 +1819,27 @@
       <c r="R16" t="n">
         <v>23.8</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S16" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>«дизельный компрессор» G10.5 (183п); «компрессоры винтовые дизельные воздушные» G7.7 (88п); «винтовой компрессор на шасси» G11.8 (67п)</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1701,12 +1894,21 @@
       <c r="R17" t="n">
         <v>23.2</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
         <is>
           <t>«генератор кислорода» G10.4 (376п); «кислородный генератор» G10.9 (196п); «кислородные генераторы» G14.7 (99п)</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1715,7 +1917,7 @@
       <c r="B18" s="3" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1765,12 +1967,21 @@
       <c r="R18" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="S18" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор 40 бар» Я10.7 (48п)</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1831,12 +2042,25 @@
       <c r="R19" t="n">
         <v>20.9</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
         <is>
           <t>«модульная компрессорная станция» G19.3 (41п); «модульная компрессорная станция мкс» G16.1 (24п); «компрессорная станция купить» G12.5 (21п)</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1897,12 +2121,25 @@
       <c r="R20" t="n">
         <v>19.7</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
         <is>
           <t>«компрессорная станция сжатого воздуха» G17.8 (31п); «компрессорные станции» Я15.5 (11п)</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1911,7 +2148,7 @@
       <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1965,12 +2202,25 @@
       <c r="R21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="S21" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t>«безмасляный компрессор купить» G15.6 (110п); «безмасляный воздушный компрессор» G18.4 (108п); «безмасляный воздушный компрессор купить» G14.9 (72п)</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1979,7 +2229,7 @@
       <c r="B22" s="3" t="inlineStr"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2033,12 +2283,21 @@
       <c r="R22" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="S22" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U22" s="3" t="inlineStr"/>
+      <c r="V22" s="3" t="inlineStr"/>
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr">
         <is>
           <t>«роторная воздуходувка» G18.3 (156п); «купить роторную воздуходувку» G5.2 (37п); «воздуходувка роторная цена» G10.6 (36п)</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr"/>
+      <c r="Y22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -2097,8 +2356,17 @@
       <c r="R23" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2159,12 +2427,21 @@
       <c r="R24" t="n">
         <v>15.9</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
         <is>
           <t>«центробежные компрессоры» G7.8 (44п); «центробежные компрессоры цена» G7.3 (36п); «центробежные компрессоры купить» G3.8 (34п)</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -2173,7 +2450,7 @@
       <c r="B25" s="3" t="inlineStr"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2227,12 +2504,25 @@
       <c r="R25" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="S25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W25" s="3" t="inlineStr"/>
+      <c r="X25" s="3" t="inlineStr">
         <is>
           <t>«безмасляный винтовой компрессор» G10.1 (118п); «винтовые безмасляные компрессоры купить» G12.6 (108п); «безмасляный винтовой компрессор купить» G9.1 (51п)</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -2241,7 +2531,7 @@
       <c r="B26" s="3" t="inlineStr"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2297,12 +2587,21 @@
       <c r="R26" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="S26" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr"/>
+      <c r="V26" s="3" t="inlineStr"/>
+      <c r="W26" s="3" t="inlineStr"/>
+      <c r="X26" s="3" t="inlineStr">
         <is>
           <t>«мембранные генераторы азота» G3.6 (33п); «промышленный генератор азота» G9.1 (21п); «генераторы азота» G8.8 (19п)</t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2363,12 +2662,27 @@
       <c r="R27" t="n">
         <v>13.1</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>«компрессор высокого давления» Я13.3 (79п); «промышленный компрессор высокого давления» G8.7 (38п); «электрический компрессор высокого давления» G3.5 (38п)</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -2377,7 +2691,7 @@
       <c r="B28" s="3" t="inlineStr"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2431,12 +2745,21 @@
       <c r="R28" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="S28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr">
         <is>
           <t>«азотная установка rdrus.ru» Я7.4 (23п); «азотная станция принцип работы» G5.5 (17п); «азотная установка принцип работы» G11.1 (14п)</t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2495,12 +2818,27 @@
       <c r="R29" t="n">
         <v>10.9</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>13</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>«то компрессоров» Я7.8 (96п); «обслуживание компрессора воздушного» Я8.9 (82п); «обслуживание компрессоров» Я8.7 (69п)</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2509,7 +2847,7 @@
       <c r="B30" s="3" t="inlineStr"/>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2559,12 +2897,25 @@
       <c r="R30" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="S30" s="3" t="inlineStr">
+      <c r="S30" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr">
         <is>
           <t>«генератор кислорода промышленный» G15.5 (35п); «генератор кислорода для лазерной резки» G4.9 (28п)</t>
         </is>
       </c>
-      <c r="T30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2623,12 +2974,25 @@
       <c r="R31" t="n">
         <v>10.7</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
         <is>
           <t>«далгакиран компрессор» G5.9 (39п); «компрессор винтовой далгакиран» G4.7 (34п); «поршневые компрессоры dalgakiran» G3.9 (26п)</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2689,12 +3053,27 @@
       <c r="R32" t="n">
         <v>10.6</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>«винтовой компрессор atlas copco» Я9.7 (119п); «компрессор atlas copco» Я10.1 (85п); «атлас копко компрессор» G7.8 (60п)</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2759,12 +3138,21 @@
       <c r="R33" s="2" t="n">
         <v>10.3</v>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>«винтовой компрессор cross air» Я10.6 (55п); «cross air винтовой компрессор купить» Я12.1 (12п)</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2825,12 +3213,21 @@
       <c r="R34" t="n">
         <v>10.3</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S34" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
         <is>
           <t>«компрессор низкого давления» Я12.6 (46п); «компрессоры. низкого. давления. воздуходувки.» G4.5 (31п); «компрессоры низкого давления» Я9.5 (24п)</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -2839,7 +3236,7 @@
       <c r="B35" s="3" t="inlineStr"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -2889,8 +3286,17 @@
       <c r="R35" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -2899,7 +3305,7 @@
       <c r="B36" s="3" t="inlineStr"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.2); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.2); кликов всего 1</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -2949,12 +3355,25 @@
       <c r="R36" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="S36" s="3" t="inlineStr">
+      <c r="S36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr">
         <is>
           <t>«поршневой безмасляный компрессор купить» G6.7 (38п); «купить безмасляный поршневой компрессор» G12.7 (28п); «поршневой безмасляный компрессор» G6.4 (26п)</t>
         </is>
       </c>
-      <c r="T36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -2963,7 +3382,7 @@
       <c r="B37" s="3" t="inlineStr"/>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория)</t>
+          <t>узкий фасет-дубль</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3019,12 +3438,27 @@
       <c r="R37" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="S37" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
         <is>
           <t>«компрессор 1000 л мин» G8.3 (92п); «компрессор 1000 л/мин» G4.8 (60п); «компрессор 1000 л мин купить» G5.0 (53п)</t>
         </is>
       </c>
-      <c r="T37" s="3" t="inlineStr"/>
+      <c r="Y37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3079,12 +3513,25 @@
       <c r="R38" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S38" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>6</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
         <is>
           <t>«винтовой компрессор ремонт» Я10.0 (144п); «винтовой компрессор ремонт promcomtech.ru/remont-vintovykh-kompressorov/» Я10.9 (50п); «ремонт винтовых компрессоров» Я8.3 (44п)</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -3093,7 +3540,7 @@
       <c r="B39" s="3" t="inlineStr"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3143,12 +3590,21 @@
       <c r="R39" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="S39" s="3" t="inlineStr">
+      <c r="S39" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="3" t="inlineStr">
         <is>
           <t>«купить винтовой компрессор» G15.6 (28п); «винтовой компрессор купить» G14.6 (26п); «винтовые компрессоры официальный сайт» G6.2 (26п)</t>
         </is>
       </c>
-      <c r="T39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -3157,7 +3613,7 @@
       <c r="B40" s="3" t="inlineStr"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3213,12 +3669,25 @@
       <c r="R40" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="S40" s="3" t="inlineStr">
+      <c r="S40" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr">
         <is>
           <t>«компрессор винтовой воздушный электрический» G14.0 (94п); «компрессоры винтовые электрические» G13.5 (89п); «компрессор воздушный винтовой электрический» G10.8 (48п)</t>
         </is>
       </c>
-      <c r="T40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3279,12 +3748,27 @@
       <c r="R41" t="n">
         <v>7.4</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>20</v>
+      </c>
+      <c r="V41" t="n">
+        <v>9</v>
+      </c>
+      <c r="W41" t="n">
+        <v>45</v>
+      </c>
+      <c r="X41" t="inlineStr">
         <is>
           <t>«компрессор центр барнаул» G7.4 (25п); «каталог компрессоров» G17.2 (12п)</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3339,12 +3823,21 @@
       <c r="R42" t="n">
         <v>7.4</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
         <is>
           <t>«рефрижераторный осушитель» Я11.3 (74п); «рефрижераторный осушитель воздуха» Я9.7 (61п)</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -3353,7 +3846,7 @@
       <c r="B43" s="3" t="inlineStr"/>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория)</t>
+          <t>узкий фасет-дубль</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3407,12 +3900,25 @@
       <c r="R43" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="S43" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr">
         <is>
           <t>«компрессор 5000 л мин» G8.4 (62п); «винтовой компрессор 5000 л мин» Я9.8 (61п); «компрессор 5 м3 мин» G8.6 (50п)</t>
         </is>
       </c>
-      <c r="T43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -3421,7 +3927,7 @@
       <c r="B44" s="3" t="inlineStr"/>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3471,8 +3977,17 @@
       <c r="R44" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="S44" s="3" t="inlineStr"/>
-      <c r="T44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3531,12 +4046,27 @@
       <c r="R45" t="n">
         <v>7.1</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S45" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>12</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X45" t="inlineStr">
         <is>
           <t>«компрессор» G14.2 (38п); «винтовой компрессор 400 литров в минуту» Я10.1 (31п); «компрессорное оборудование купить» Я10.2 (28п)</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -3545,7 +4075,7 @@
       <c r="B46" s="3" t="inlineStr"/>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.2); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.2); кликов всего 1</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3595,12 +4125,21 @@
       <c r="R46" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="S46" s="3" t="inlineStr">
+      <c r="S46" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор cross air» G8.0 (70п); «винтовой компрессор кросс аир» G6.4 (28п); «кросс аир компрессор» G6.6 (14п)</t>
         </is>
       </c>
-      <c r="T46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -3609,7 +4148,7 @@
       <c r="B47" s="3" t="inlineStr"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория)</t>
+          <t>узкий фасет-дубль</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3663,12 +4202,25 @@
       <c r="R47" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="S47" s="3" t="inlineStr">
+      <c r="S47" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr">
         <is>
           <t>«компрессор 500 литров в минуту» G8.6 (73п); «компрессор 500л» G11.2 (48п); «компрессор 500 л мин цена» G10.7 (45п)</t>
         </is>
       </c>
-      <c r="T47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -3677,7 +4229,7 @@
       <c r="B48" s="3" t="inlineStr"/>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3727,12 +4279,21 @@
       <c r="R48" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="S48" s="3" t="inlineStr">
+      <c r="S48" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr">
         <is>
           <t>«дизельные компрессоры атлас» Я9.1 (30п); «компрессор дизельный атлас копко» Я8.8 (15п)</t>
         </is>
       </c>
-      <c r="T48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3791,12 +4352,27 @@
       <c r="R49" t="n">
         <v>5.7</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>11</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W49" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="X49" t="inlineStr">
         <is>
           <t>«компрессор для лазерной резки металла» G9.5 (55п); «винтовой компрессор для лазерного станка» G10.8 (54п); «компрессор для лазерного гравера» G8.9 (53п)</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3851,12 +4427,27 @@
       <c r="R50" t="n">
         <v>5.4</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S50" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>11</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
         <is>
           <t>«компрессор высокого давления 300 бар» G8.6 (67п); «компрессор высокого давления 300 атм купить» G8.5 (45п); «компрессор 300 бар» G7.6 (41п)</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -3865,7 +4456,7 @@
       <c r="B51" s="3" t="inlineStr"/>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -3915,12 +4506,21 @@
       <c r="R51" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="S51" s="3" t="inlineStr">
+      <c r="S51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr"/>
+      <c r="W51" s="3" t="inlineStr"/>
+      <c r="X51" s="3" t="inlineStr">
         <is>
           <t>«взрывозащищенные компрессоры» Я8.4 (25п)</t>
         </is>
       </c>
-      <c r="T51" s="3" t="inlineStr"/>
+      <c r="Y51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -3929,7 +4529,7 @@
       <c r="B52" s="3" t="inlineStr"/>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -3979,12 +4579,21 @@
       <c r="R52" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="S52" s="3" t="inlineStr">
+      <c r="S52" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T52" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" s="3" t="inlineStr"/>
+      <c r="W52" s="3" t="inlineStr"/>
+      <c r="X52" s="3" t="inlineStr">
         <is>
           <t>«осушитель воздуха с охлаждением» Я7.8 (11п)</t>
         </is>
       </c>
-      <c r="T52" s="3" t="inlineStr"/>
+      <c r="Y52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4043,12 +4652,21 @@
       <c r="R53" t="n">
         <v>4.8</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
         <is>
           <t>«винтовой мини компрессор» Я7.5 (21п); «компрессор миниатюрный винтовой» Я7.7 (21п)</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4103,12 +4721,21 @@
       <c r="R54" t="n">
         <v>4.8</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
         <is>
           <t>«компрессор atlas copco ga11ff» Я6.9 (57п)</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4163,12 +4790,21 @@
       <c r="R55" t="n">
         <v>4.8</v>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
         <is>
           <t>«винтовой компрессор 37 квт» Я6.4 (28п)</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -4177,7 +4813,7 @@
       <c r="B56" s="3" t="inlineStr"/>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.8); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.8); кликов всего 1</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -4227,12 +4863,21 @@
       <c r="R56" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="S56" s="3" t="inlineStr">
+      <c r="S56" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" s="3" t="inlineStr"/>
+      <c r="V56" s="3" t="inlineStr"/>
+      <c r="W56" s="3" t="inlineStr"/>
+      <c r="X56" s="3" t="inlineStr">
         <is>
           <t>«компрессор дизельный передвижной атлас копко» Я10.6 (43п); «дизельные компрессоры atlas copco купить» Я11.6 (16п)</t>
         </is>
       </c>
-      <c r="T56" s="3" t="inlineStr"/>
+      <c r="Y56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4293,12 +4938,27 @@
       <c r="R57" t="n">
         <v>4</v>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>19</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="inlineStr">
         <is>
           <t>«дожимной компрессор» G10.9 (67п); «компрессор» Я17.5 (38п)</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4357,12 +5017,21 @@
       <c r="R58" t="n">
         <v>4</v>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S58" t="n">
+        <v>4</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
         <is>
           <t>«компрессор atlas copco» Я11.7 (129п); «компрессор atlas copco ga» Я8.5 (99п); «atlas copco компрессор» Я11.3 (77п)</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4417,12 +5086,21 @@
       <c r="R59" t="n">
         <v>4</v>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
         <is>
           <t>«ркз компрессор официальный сайт» Я7.5 (25п); «ркз компрессор» Я9.8 (19п)</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -4431,7 +5109,7 @@
       <c r="B60" s="3" t="inlineStr"/>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория)</t>
+          <t>узкий фасет-дубль</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -4487,12 +5165,25 @@
       <c r="R60" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="S60" s="3" t="inlineStr">
+      <c r="S60" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3" t="inlineStr"/>
+      <c r="X60" s="3" t="inlineStr">
         <is>
           <t>«компрессор винтовой 1500 л мин» Я10.6 (65п); «компрессор 1500 л мин» G13.0 (48п); «компрессор 1500 л мин цена» G10.4 (36п)</t>
         </is>
       </c>
-      <c r="T60" s="3" t="inlineStr"/>
+      <c r="Y60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4553,12 +5244,25 @@
       <c r="R61" t="n">
         <v>3.6</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S61" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>7</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
         <is>
           <t>«компрессор воздушный 12 атмосфер» G8.7 (36п); «компрессоры 12 атмосфер» G5.4 (29п); «компрессоры 12 квт» G3.8 (26п)</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -4567,7 +5271,7 @@
       <c r="B62" s="3" t="inlineStr"/>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -4621,12 +5325,25 @@
       <c r="R62" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="S62" s="3" t="inlineStr">
+      <c r="S62" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" s="3" t="inlineStr"/>
+      <c r="X62" s="3" t="inlineStr">
         <is>
           <t>«компрессор промышленный» G17.4 (114п); «компрессор воздушный промышленный» G17.9 (70п); «компрессор промышленный купить» G15.7 (62п)</t>
         </is>
       </c>
-      <c r="T62" s="3" t="inlineStr"/>
+      <c r="Y62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -4635,7 +5352,7 @@
       <c r="B63" s="3" t="inlineStr"/>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.8); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.8); кликов всего 1</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -4685,12 +5402,21 @@
       <c r="R63" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="S63" s="3" t="inlineStr">
+      <c r="S63" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T63" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U63" s="3" t="inlineStr"/>
+      <c r="V63" s="3" t="inlineStr"/>
+      <c r="W63" s="3" t="inlineStr"/>
+      <c r="X63" s="3" t="inlineStr">
         <is>
           <t>«цена передвижные компрессоры» Я10.7 (13п); «купить передвижные компрессоры» Я10.9 (10п)</t>
         </is>
       </c>
-      <c r="T63" s="3" t="inlineStr"/>
+      <c r="Y63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4753,12 +5479,21 @@
       <c r="R64" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="S64" s="2" t="inlineStr">
+      <c r="S64" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>«компрессор atlas copco» Я10.7 (51п); «компрессорное оборудование atlas сopco» Я8.8 (48п); «компрессор atlas copco gk-inergo.ru» Я8.5 (27п)</t>
         </is>
       </c>
-      <c r="T64" s="2" t="inlineStr"/>
+      <c r="Y64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4813,12 +5548,21 @@
       <c r="R65" t="n">
         <v>3.6</v>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
         <is>
           <t>«винтовой компрессор 55 квт» Я6.7 (32п)</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4873,12 +5617,21 @@
       <c r="R66" t="n">
         <v>3.6</v>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S66" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
         <is>
           <t>«дизельный компрессор atlas copco» Я9.8 (127п); «дизельные компрессоры xas» Я8.7 (110п); «дизельный компрессор atlas» Я8.4 (110п)</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4939,12 +5692,27 @@
       <c r="R67" t="n">
         <v>3.5</v>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S67" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>32</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X67" t="inlineStr">
         <is>
           <t>«осушитель сжатого воздуха для компрессора» G9.6 (102п); «осушитель сжатого воздуха» G17.5 (84п); «осушитель для компрессора цена» G4.8 (39п)</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>ПИЛОТ</t>
         </is>
@@ -5003,12 +5771,21 @@
       <c r="R68" t="n">
         <v>3.5</v>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
         <is>
           <t>«модульная компрессорная станция» Я10.7 (16п)</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -5017,7 +5794,7 @@
       <c r="B69" s="3" t="inlineStr"/>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -5067,12 +5844,21 @@
       <c r="R69" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="S69" s="3" t="inlineStr">
+      <c r="S69" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T69" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U69" s="3" t="inlineStr"/>
+      <c r="V69" s="3" t="inlineStr"/>
+      <c r="W69" s="3" t="inlineStr"/>
+      <c r="X69" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор cross air» Я10.5 (92п); «винтовой компрессор кросс аир» Я10.2 (26п); «cross air компрессор винтовой» Я10.4 (20п)</t>
         </is>
       </c>
-      <c r="T69" s="3" t="inlineStr"/>
+      <c r="Y69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -5081,7 +5867,7 @@
       <c r="B70" s="3" t="inlineStr"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -5137,12 +5923,25 @@
       <c r="R70" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="S70" s="3" t="inlineStr">
+      <c r="S70" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W70" s="3" t="inlineStr"/>
+      <c r="X70" s="3" t="inlineStr">
         <is>
           <t>«рефрижераторный осушитель воздуха» G18.8 (53п); «рефрижераторный осушитель сжатого воздуха» G18.8 (45п); «осушитель рефрижераторного типа купить» G10.5 (44п)</t>
         </is>
       </c>
-      <c r="T70" s="3" t="inlineStr"/>
+      <c r="Y70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -5151,7 +5950,7 @@
       <c r="B71" s="3" t="inlineStr"/>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория); кликов всего 1 — статистики нет</t>
+          <t>узкий фасет-дубль; кликов всего 1</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -5201,12 +6000,21 @@
       <c r="R71" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="S71" s="3" t="inlineStr">
+      <c r="S71" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" s="3" t="inlineStr"/>
+      <c r="V71" s="3" t="inlineStr"/>
+      <c r="W71" s="3" t="inlineStr"/>
+      <c r="X71" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор 5000 л мин» Я15.3 (72п); «винтовой компрессор 5000 л мин цена» Я8.3 (19п)</t>
         </is>
       </c>
-      <c r="T71" s="3" t="inlineStr"/>
+      <c r="Y71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -5215,7 +6023,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -5265,12 +6073,21 @@
       <c r="R72" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="S72" s="3" t="inlineStr">
+      <c r="S72" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T72" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U72" s="3" t="inlineStr"/>
+      <c r="V72" s="3" t="inlineStr"/>
+      <c r="W72" s="3" t="inlineStr"/>
+      <c r="X72" s="3" t="inlineStr">
         <is>
           <t>«осушители воздуха аирфловер» Я10.6 (21п)</t>
         </is>
       </c>
-      <c r="T72" s="3" t="inlineStr"/>
+      <c r="Y72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -5279,7 +6096,7 @@
       <c r="B73" s="3" t="inlineStr"/>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -5329,12 +6146,21 @@
       <c r="R73" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="S73" s="3" t="inlineStr">
+      <c r="S73" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T73" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U73" s="3" t="inlineStr"/>
+      <c r="V73" s="3" t="inlineStr"/>
+      <c r="W73" s="3" t="inlineStr"/>
+      <c r="X73" s="3" t="inlineStr">
         <is>
           <t>«компрессор воздушный передвижной» Я11.8 (17п); «компрессор воздушный дизельный» Я10.6 (14п); «компрессор мобильный дизельный» Я11.6 (11п)</t>
         </is>
       </c>
-      <c r="T73" s="3" t="inlineStr"/>
+      <c r="Y73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5395,12 +6221,27 @@
       <c r="R74" t="n">
         <v>3.2</v>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>38</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W74" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X74" t="inlineStr">
         <is>
           <t>«ресивер для компрессора» G14.7 (81п); «воздушный ресивер» G16.0 (68п); «купить ресивер для воздуха» G4.2 (41п)</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -5409,7 +6250,7 @@
       <c r="B75" s="3" t="inlineStr"/>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -5459,12 +6300,21 @@
       <c r="R75" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="S75" s="3" t="inlineStr">
+      <c r="S75" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" s="3" t="inlineStr"/>
+      <c r="V75" s="3" t="inlineStr"/>
+      <c r="W75" s="3" t="inlineStr"/>
+      <c r="X75" s="3" t="inlineStr">
         <is>
           <t>«компрессоры для производства» Я17.2 (60п)</t>
         </is>
       </c>
-      <c r="T75" s="3" t="inlineStr"/>
+      <c r="Y75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -5473,7 +6323,7 @@
       <c r="B76" s="3" t="inlineStr"/>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория); кликов всего 1 — статистики нет</t>
+          <t>узкий фасет-дубль; кликов всего 1</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -5523,8 +6373,21 @@
       <c r="R76" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="S76" s="3" t="inlineStr"/>
-      <c r="T76" s="3" t="inlineStr"/>
+      <c r="S76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="3" t="inlineStr"/>
+      <c r="X76" s="3" t="inlineStr"/>
+      <c r="Y76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -5533,7 +6396,7 @@
       <c r="B77" s="3" t="inlineStr"/>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -5583,12 +6446,21 @@
       <c r="R77" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="S77" s="3" t="inlineStr">
+      <c r="S77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" s="3" t="inlineStr"/>
+      <c r="V77" s="3" t="inlineStr"/>
+      <c r="W77" s="3" t="inlineStr"/>
+      <c r="X77" s="3" t="inlineStr">
         <is>
           <t>«компрессор для пескоструя» Я16.1 (33п); «компрессор винтовой для пескоструя» Я17.6 (24п)</t>
         </is>
       </c>
-      <c r="T77" s="3" t="inlineStr"/>
+      <c r="Y77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -5597,7 +6469,7 @@
       <c r="B78" s="3" t="inlineStr"/>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -5647,12 +6519,21 @@
       <c r="R78" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="S78" s="3" t="inlineStr">
+      <c r="S78" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" s="3" t="inlineStr"/>
+      <c r="V78" s="3" t="inlineStr"/>
+      <c r="W78" s="3" t="inlineStr"/>
+      <c r="X78" s="3" t="inlineStr">
         <is>
           <t>«компрессоры воздушные ремезов» Я12.5 (34п)</t>
         </is>
       </c>
-      <c r="T78" s="3" t="inlineStr"/>
+      <c r="Y78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -5661,7 +6542,7 @@
       <c r="B79" s="3" t="inlineStr"/>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -5711,12 +6592,21 @@
       <c r="R79" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="S79" s="3" t="inlineStr">
+      <c r="S79" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U79" s="3" t="inlineStr"/>
+      <c r="V79" s="3" t="inlineStr"/>
+      <c r="W79" s="3" t="inlineStr"/>
+      <c r="X79" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор на ресивере» G15.4 (27п)</t>
         </is>
       </c>
-      <c r="T79" s="3" t="inlineStr"/>
+      <c r="Y79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -5725,7 +6615,7 @@
       <c r="B80" s="3" t="inlineStr"/>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -5775,8 +6665,17 @@
       <c r="R80" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="S80" s="3" t="inlineStr"/>
-      <c r="T80" s="3" t="inlineStr"/>
+      <c r="S80" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" s="3" t="inlineStr"/>
+      <c r="V80" s="3" t="inlineStr"/>
+      <c r="W80" s="3" t="inlineStr"/>
+      <c r="X80" s="3" t="inlineStr"/>
+      <c r="Y80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -5785,7 +6684,7 @@
       <c r="B81" s="3" t="inlineStr"/>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -5839,12 +6738,21 @@
       <c r="R81" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="S81" s="3" t="inlineStr">
+      <c r="S81" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" s="3" t="inlineStr"/>
+      <c r="V81" s="3" t="inlineStr"/>
+      <c r="W81" s="3" t="inlineStr"/>
+      <c r="X81" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор atlas copco» Я11.7 (190п); «купить винтовой компрессор атлас копко» Я11.3 (47п); «винтовой компрессор атлас копко» Я10.6 (46п)</t>
         </is>
       </c>
-      <c r="T81" s="3" t="inlineStr"/>
+      <c r="Y81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -5853,7 +6761,7 @@
       <c r="B82" s="3" t="inlineStr"/>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -5903,12 +6811,21 @@
       <c r="R82" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="S82" s="3" t="inlineStr">
+      <c r="S82" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U82" s="3" t="inlineStr"/>
+      <c r="V82" s="3" t="inlineStr"/>
+      <c r="W82" s="3" t="inlineStr"/>
+      <c r="X82" s="3" t="inlineStr">
         <is>
           <t>«адсорбционный осушитель» Я16.5 (18п)</t>
         </is>
       </c>
-      <c r="T82" s="3" t="inlineStr"/>
+      <c r="Y82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -5917,7 +6834,7 @@
       <c r="B83" s="3" t="inlineStr"/>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -5967,12 +6884,21 @@
       <c r="R83" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="S83" s="3" t="inlineStr">
+      <c r="S83" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" s="3" t="inlineStr"/>
+      <c r="V83" s="3" t="inlineStr"/>
+      <c r="W83" s="3" t="inlineStr"/>
+      <c r="X83" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор atlas» Я10.1 (30п); «винтовой компрессор atlas copco авито» Я10.5 (12п); «купить винтовой компрессор атлас копко» Я10.9 (11п)</t>
         </is>
       </c>
-      <c r="T83" s="3" t="inlineStr"/>
+      <c r="Y83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -5981,7 +6907,7 @@
       <c r="B84" s="3" t="inlineStr"/>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -6031,12 +6957,21 @@
       <c r="R84" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="S84" s="3" t="inlineStr">
+      <c r="S84" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U84" s="3" t="inlineStr"/>
+      <c r="V84" s="3" t="inlineStr"/>
+      <c r="W84" s="3" t="inlineStr"/>
+      <c r="X84" s="3" t="inlineStr">
         <is>
           <t>«рефрижераторный осушитель» G15.6 (31п); «осушитель рефрижераторный» G9.2 (17п); «рефрижераторный осушитель воздуха» G11.4 (15п)</t>
         </is>
       </c>
-      <c r="T84" s="3" t="inlineStr"/>
+      <c r="Y84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -6045,7 +6980,7 @@
       <c r="B85" s="3" t="inlineStr"/>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.2); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.2); кликов всего 1</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -6099,12 +7034,21 @@
       <c r="R85" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="S85" s="3" t="inlineStr">
+      <c r="S85" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T85" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U85" s="3" t="inlineStr"/>
+      <c r="V85" s="3" t="inlineStr"/>
+      <c r="W85" s="3" t="inlineStr"/>
+      <c r="X85" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор 40 бар» G11.1 (67п); «дожимной компрессор высокого давления» G7.5 (43п); «дожимной компрессор 40 бар» G3.9 (33п)</t>
         </is>
       </c>
-      <c r="T85" s="3" t="inlineStr"/>
+      <c r="Y85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -6113,7 +7057,7 @@
       <c r="B86" s="3" t="inlineStr"/>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.2); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.2); кликов всего 1</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -6163,12 +7107,21 @@
       <c r="R86" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="S86" s="3" t="inlineStr">
+      <c r="S86" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U86" s="3" t="inlineStr"/>
+      <c r="V86" s="3" t="inlineStr"/>
+      <c r="W86" s="3" t="inlineStr"/>
+      <c r="X86" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор для лазерной резки» G5.2 (15п)</t>
         </is>
       </c>
-      <c r="T86" s="3" t="inlineStr"/>
+      <c r="Y86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -6177,7 +7130,7 @@
       <c r="B87" s="3" t="inlineStr"/>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория); кликов всего 1 — статистики нет</t>
+          <t>узкий фасет-дубль; кликов всего 1</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -6231,12 +7184,25 @@
       <c r="R87" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S87" s="3" t="inlineStr">
+      <c r="S87" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3" t="inlineStr"/>
+      <c r="X87" s="3" t="inlineStr">
         <is>
           <t>«компрессор 12000 л/мин» G5.2 (32п); «компрессоры 12000 л/мин» G3.7 (31п); «компрессор 75 квт» G11.1 (24п)</t>
         </is>
       </c>
-      <c r="T87" s="3" t="inlineStr"/>
+      <c r="Y87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -6245,7 +7211,7 @@
       <c r="B88" s="3" t="inlineStr"/>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -6299,12 +7265,27 @@
       <c r="R88" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="S88" s="3" t="inlineStr">
+      <c r="S88" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W88" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X88" s="3" t="inlineStr">
         <is>
           <t>«ремонт винтового компрессора» G11.1 (73п); «ремонт винтового блока компрессора» Я9.0 (32п); «ремонт винтовых блоков» Я10.1 (23п)</t>
         </is>
       </c>
-      <c r="T88" s="3" t="inlineStr"/>
+      <c r="Y88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -6313,7 +7294,7 @@
       <c r="B89" s="3" t="inlineStr"/>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория); кликов всего 1 — статистики нет</t>
+          <t>узкий фасет-дубль; кликов всего 1</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -6367,12 +7348,25 @@
       <c r="R89" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="S89" s="3" t="inlineStr">
+      <c r="S89" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="inlineStr"/>
+      <c r="X89" s="3" t="inlineStr">
         <is>
           <t>«компрессор 15 бар» G10.3 (45п); «винтовой компрессор 15 м3 мин» Я7.9 (33п); «купить компрессор 15 атмосфер» G9.6 (30п)</t>
         </is>
       </c>
-      <c r="T89" s="3" t="inlineStr"/>
+      <c r="Y89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
@@ -6381,7 +7375,7 @@
       <c r="B90" s="3" t="inlineStr"/>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -6435,12 +7429,25 @@
       <c r="R90" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="S90" s="3" t="inlineStr">
+      <c r="S90" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="3" t="inlineStr"/>
+      <c r="X90" s="3" t="inlineStr">
         <is>
           <t>«компрессор 20 бар» G11.9 (30п); «компрессор 20 бар цена» G8.5 (24п); «купить компрессор 20 атмосфер» G8.2 (24п)</t>
         </is>
       </c>
-      <c r="T90" s="3" t="inlineStr"/>
+      <c r="Y90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -6449,7 +7456,7 @@
       <c r="B91" s="3" t="inlineStr"/>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 2 — статистики нет</t>
+          <t>кликов всего 2</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -6505,12 +7512,25 @@
       <c r="R91" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="S91" s="3" t="inlineStr">
+      <c r="S91" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="inlineStr"/>
+      <c r="X91" s="3" t="inlineStr">
         <is>
           <t>«адсорбционный осушитель» G12.3 (127п); «адсорбционный осушитель воздуха» G19.7 (104п); «адсорбционный осушитель воздуха купить» G15.6 (59п)</t>
         </is>
       </c>
-      <c r="T91" s="3" t="inlineStr"/>
+      <c r="Y91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -6519,7 +7539,7 @@
       <c r="B92" s="3" t="inlineStr"/>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -6569,8 +7589,21 @@
       <c r="R92" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="S92" s="3" t="inlineStr"/>
-      <c r="T92" s="3" t="inlineStr"/>
+      <c r="S92" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3" t="inlineStr"/>
+      <c r="X92" s="3" t="inlineStr"/>
+      <c r="Y92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
@@ -6579,7 +7612,7 @@
       <c r="B93" s="3" t="inlineStr"/>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>кликов всего 1 — статистики нет</t>
+          <t>кликов всего 1</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -6629,12 +7662,25 @@
       <c r="R93" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="S93" s="3" t="inlineStr">
+      <c r="S93" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3" t="inlineStr"/>
+      <c r="X93" s="3" t="inlineStr">
         <is>
           <t>«ремонт осушителя воздуха для компрессора» Я14.9 (15п)</t>
         </is>
       </c>
-      <c r="T93" s="3" t="inlineStr"/>
+      <c r="Y93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -6643,7 +7689,7 @@
       <c r="B94" s="3" t="inlineStr"/>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -6697,12 +7743,21 @@
       <c r="R94" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="S94" s="3" t="inlineStr">
+      <c r="S94" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T94" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U94" s="3" t="inlineStr"/>
+      <c r="V94" s="3" t="inlineStr"/>
+      <c r="W94" s="3" t="inlineStr"/>
+      <c r="X94" s="3" t="inlineStr">
         <is>
           <t>«винтовой компрессор cross air» G14.8 (24п); «компрессор cross air» G13.6 (13п)</t>
         </is>
       </c>
-      <c r="T94" s="3" t="inlineStr"/>
+      <c r="Y94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -6711,7 +7766,7 @@
       <c r="B95" s="3" t="inlineStr"/>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>служебная; микро-потенциал (gain 1.8); кликов всего 1 — статистики нет</t>
+          <t>служебная; микро-потенциал (gain 1.8); кликов всего 1</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -6761,12 +7816,25 @@
       <c r="R95" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="S95" s="3" t="inlineStr">
+      <c r="S95" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="3" t="inlineStr"/>
+      <c r="X95" s="3" t="inlineStr">
         <is>
           <t>«обслуживание компрессора» Я10.2 (22п); «компрессор тех центр serviceset» Я4.2 (19п); «установка и обслуживание компрессоров» Я5.9 (19п)</t>
         </is>
       </c>
-      <c r="T95" s="3" t="inlineStr"/>
+      <c r="Y95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -6775,7 +7843,7 @@
       <c r="B96" s="3" t="inlineStr"/>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.5); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.5); кликов всего 1</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -6825,12 +7893,21 @@
       <c r="R96" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="S96" s="3" t="inlineStr">
+      <c r="S96" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T96" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U96" s="3" t="inlineStr"/>
+      <c r="V96" s="3" t="inlineStr"/>
+      <c r="W96" s="3" t="inlineStr"/>
+      <c r="X96" s="3" t="inlineStr">
         <is>
           <t>«аргус компрессор» Я10.9 (14п)</t>
         </is>
       </c>
-      <c r="T96" s="3" t="inlineStr"/>
+      <c r="Y96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -6839,7 +7916,7 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>главная; микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>главная; микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -6893,12 +7970,21 @@
       <c r="R97" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="S97" s="2" t="inlineStr">
+      <c r="S97" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>«компрессор авас» G9.1 (31п); «компрессор винтовой авас» Я9.6 (23п)</t>
         </is>
       </c>
-      <c r="T97" s="2" t="inlineStr"/>
+      <c r="Y97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -6907,7 +7993,7 @@
       <c r="B98" s="3" t="inlineStr"/>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -6957,12 +8043,21 @@
       <c r="R98" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="S98" s="3" t="inlineStr">
+      <c r="S98" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="3" t="inlineStr"/>
+      <c r="V98" s="3" t="inlineStr"/>
+      <c r="W98" s="3" t="inlineStr"/>
+      <c r="X98" s="3" t="inlineStr">
         <is>
           <t>«atlas copco компрессор» Я10.7 (51п); «компрессор atlas copco gx11ff» Я10.8 (32п)</t>
         </is>
       </c>
-      <c r="T98" s="3" t="inlineStr"/>
+      <c r="Y98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -6971,7 +8066,7 @@
       <c r="B99" s="3" t="inlineStr"/>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>служебная; микро-потенциал (gain 1.6); кликов всего 1 — статистики нет</t>
+          <t>служебная; микро-потенциал (gain 1.6); кликов всего 1</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -7021,12 +8116,21 @@
       <c r="R99" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="S99" s="3" t="inlineStr">
+      <c r="S99" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" s="3" t="inlineStr"/>
+      <c r="V99" s="3" t="inlineStr"/>
+      <c r="W99" s="3" t="inlineStr"/>
+      <c r="X99" s="3" t="inlineStr">
         <is>
           <t>«компрессор атлас копко обслуживание» Я7.9 (15п)</t>
         </is>
       </c>
-      <c r="T99" s="3" t="inlineStr"/>
+      <c r="Y99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -7035,7 +8139,7 @@
       <c r="B100" s="3" t="inlineStr"/>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>микро-потенциал (gain 1.2); кликов всего 1 — статистики нет</t>
+          <t>микро-потенциал (gain 1.2); кликов всего 1</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -7089,12 +8193,25 @@
       <c r="R100" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="S100" s="3" t="inlineStr">
+      <c r="S100" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W100" s="3" t="inlineStr"/>
+      <c r="X100" s="3" t="inlineStr">
         <is>
           <t>«компрессор 15 бар» G7.6 (50п); «винтовой компрессор 15 бар» G8.2 (38п); «компрессор воздушный 15 бар» G8.0 (21п)</t>
         </is>
       </c>
-      <c r="T100" s="3" t="inlineStr"/>
+      <c r="Y100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
@@ -7103,7 +8220,7 @@
       <c r="B101" s="3" t="inlineStr"/>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>узкий фасет-дубль (та же сущность, что родительская категория); микро-потенциал (gain 1.2); кликов всего 1 — статистики нет</t>
+          <t>узкий фасет-дубль; микро-потенциал (gain 1.2); кликов всего 1</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -7153,12 +8270,25 @@
       <c r="R101" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="S101" s="3" t="inlineStr">
+      <c r="S101" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V101" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W101" s="3" t="inlineStr"/>
+      <c r="X101" s="3" t="inlineStr">
         <is>
           <t>«компрессор 3000 л мин» G7.2 (60п); «компрессор 3000 литров в минуту» G6.3 (46п); «винтовой компрессор 3000 л мин» G6.8 (45п)</t>
         </is>
       </c>
-      <c r="T101" s="3" t="inlineStr"/>
+      <c r="Y101" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seo-texts/frog/acceptor-top100.xlsx
+++ b/seo-texts/frog/acceptor-top100.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,6 +39,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,10 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -547,7 +553,6 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/vintovye_kompressory</t>
@@ -617,7 +622,6 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/kislorodnye-ustanovki</t>
@@ -687,7 +691,6 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/osushiteli_vozdukha/adsorbtsionnye_osushiteli</t>
@@ -757,7 +760,6 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/bezmaslyanye_kompressory</t>
@@ -795,7 +797,6 @@
       <c r="L5" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>7</v>
       </c>
@@ -825,7 +826,6 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/azotnye-ustanovki</t>
@@ -895,7 +895,6 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-200-bar</t>
@@ -957,282 +956,230 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/dizelnye-kompressory</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Дизельные/передвижные</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1335169</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ок</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Модульные/блочные КС</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>2189896</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>«компрессорная станция сжатого воздуха» G17.8; «компрессорные станции» Я15.5</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>поднята владельцем 05.08 в ядро (была резерв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L8" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>18</v>
-      </c>
-      <c r="N8" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>«дизель компрессор» Я10.1; «дизельный передвижной компрессор promcomtech.ru/catalog/dizelnye-kompressory/peredvizhnye/» Я7.1; «компрессор высокого давления дизельный» Я6.7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>агент: качать</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>служебная</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/services</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha/mks</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>не проверить</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="K9" s="2" t="n">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Модульные/блочные КС</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>2189896</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="K9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="2" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>«ремонт и обслуживание компрессоров» G10.9; «техническое обслуживание компрессоров теплообменников» Я5.0; «обслуживание винтовых компрессоров» G16.0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>агент: качать</t>
+      <c r="L9" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>«модульная компрессорная станция» G19.3; «модульная компрессорная станция мкс» G16.1; «компрессорная станция купить» G12.5</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>поднята владельцем 05.08 в ядро (была резерв)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Азотные станции</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2451874</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ок</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="P10" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>«генератор азота цена» G18.2; «генератор азота» G14.1; «адсорбционный генератор азота» G7.6</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>агент: качать</t>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha/mobilnye-kompressornye-stantsii</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Модульные/блочные КС</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2189896</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>прокси: сегмент КС</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>ДОБАВЛЕНО ВЛАДЕЛЬЦЕМ 05.08: замеров нет (страницы не попали в выгрузку Вебмастера) - позиции/клики неизвестны, приоритет назначен вручную</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha/dozhimnye-stantsii</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Винтовые</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1523189</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ок</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="M11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор» G15.0; «стоимость винтового компрессора» G10.7; «компрессор промышленный винтовой» G15.7</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>агент: качать</t>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Модульные/блочные КС</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2189896</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>прокси: сегмент КС</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>ДОБАВЛЕНО ВЛАДЕЛЬЦЕМ 05.08: замеров нет (страницы не попали в выгрузку Вебмастера) - позиции/клики неизвестны, приоритет назначен вручную</t>
         </is>
       </c>
     </row>
@@ -1245,10 +1192,9 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli</t>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/dizelnye-kompressory</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1258,46 +1204,46 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1004759</v>
+        <v>1335169</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>завышен</t>
+          <t>ок</t>
         </is>
       </c>
       <c r="J12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="K12" t="n">
-        <v>19</v>
-      </c>
       <c r="L12" t="n">
-        <v>23.8</v>
+        <v>12.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
-        <v>24.4</v>
+        <v>29.4</v>
       </c>
       <c r="O12" t="n">
-        <v>36.7</v>
+        <v>58.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.5</v>
+        <v>39.3</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>«рефрижераторный осушитель воздуха» G6.4; «осушитель рефрижераторного типа» G5.8; «осушитель сжатого воздуха рефрижераторного типа» G5.5</t>
+          <t>«дизель компрессор» Я10.1; «дизельный передвижной компрессор promcomtech.ru/catalog/dizelnye-kompressory/peredvizhnye/» Я7.1; «компрессор высокого давления дизельный» Я6.7</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1315,15 +1261,19 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>служебная</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/mks</t>
+          <t>https://prokompressor.ru/services</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1332,41 +1282,49 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1335169</v>
+        <v>808032</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>не проверить</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>8.6</v>
+        <v>28.2</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="N13" t="n">
-        <v>15.9</v>
+        <v>58.5</v>
       </c>
       <c r="O13" t="n">
-        <v>31.8</v>
+        <v>47.2</v>
       </c>
       <c r="P13" t="n">
-        <v>21.2</v>
+        <v>47.2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>«модульные компрессорные станции» G6.4; «модульная компрессорная станция мкс» G8.3; «компрессорная» G8.3</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+          <t>«ремонт и обслуживание компрессоров» G10.9; «техническое обслуживание компрессоров теплообменников» Я5.0; «обслуживание винтовых компрессоров» G16.0</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>агент: качать</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1377,58 +1335,59 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/dizelnye</t>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Азотные станции</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2355138</v>
+        <v>2451874</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ок</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>9.300000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="O14" t="n">
-        <v>23.8</v>
+        <v>42.9</v>
       </c>
       <c r="P14" t="n">
-        <v>23.8</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>«дизельный компрессор» G10.5; «компрессоры винтовые дизельные воздушные» G7.7; «винтовой компрессор на шасси» G11.8</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+          <t>«генератор азота цена» G18.2; «генератор азота» G14.1; «адсорбционный генератор азота» G7.6</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>агент: качать</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1439,116 +1398,134 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/kislorodnye-ustanovki/generator-kisloroda</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Винтовые</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1523189</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ок</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>«винтовой компрессор» G15.0; «стоимость винтового компрессора» G10.7; «компрессор промышленный винтовой» G15.7</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>агент: качать</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ЯДРО</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>enger-air.ru</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Кислородные станции</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>2451874</v>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Осушители</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1004759</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>битрикс-бренд+кат.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>«генератор кислорода» G10.4; «кислородный генератор» G10.9; «кислородные генераторы» G14.7</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>ЯДРО</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/kompressory-40-bar</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Винтовые</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>12986897</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>payload</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M16" s="2" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>завышен</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>19</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор 40 бар» Я10.7</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>«рефрижераторный осушитель воздуха» G6.4; «осушитель рефрижераторного типа» G5.8; «осушитель сжатого воздуха рефрижераторного типа» G5.5</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>агент: качать</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1556,61 +1533,58 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>резерв</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>ЯДРО</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha/mks</t>
+          <t>https://enger-air.ru/catalog/mks</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Модульные/блочные КС</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2189896</v>
+        <v>1335169</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
       <c r="J17" t="n">
-        <v>19.4</v>
+        <v>8.6</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>9.5</v>
+        <v>15.9</v>
       </c>
       <c r="O17" t="n">
-        <v>20.9</v>
+        <v>31.8</v>
       </c>
       <c r="P17" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>«модульная компрессорная станция» G19.3; «модульная компрессорная станция мкс» G16.1; «компрессорная станция купить» G12.5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+          <t>«модульные компрессорные станции» G6.4; «модульная компрессорная станция мкс» G8.3; «компрессорная» G8.3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1618,257 +1592,248 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>ЯДРО</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/dizelnye</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Дизельные/передвижные</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2355138</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>«дизельный компрессор» G10.5; «компрессоры винтовые дизельные воздушные» G7.7; «винтовой компрессор на шасси» G11.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ЯДРО</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/kislorodnye-ustanovki/generator-kisloroda</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Кислородные станции</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2451874</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>«генератор кислорода» G10.4; «кислородный генератор» G10.9; «кислородные генераторы» G14.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ЯДРО</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/kompressory-40-bar</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Винтовые</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>12986897</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>«винтовой компрессор 40 бар» Я10.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>резерв</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-bezmaslyanye</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Модульные/блочные КС</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>2189896</v>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Безмасляные/центробежные</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>8567838</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>битрикс-катег.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J21" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>«компрессорная станция сжатого воздуха» G17.8; «компрессорные станции» Я15.5</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>резерв</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-bezmaslyanye</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Безмасляные/центробежные</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>8567838</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="n">
+      <c r="L21" t="n">
         <v>38.1</v>
       </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="n">
+      <c r="N21" t="n">
         <v>2.1</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="O21" t="n">
         <v>18.4</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="P21" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>«безмасляный компрессор купить» G15.6; «безмасляный воздушный компрессор» G18.4; «безмасляный воздушный компрессор купить» G14.9</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>резерв</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/rotornye-vozdukhoduvki</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Воздуходувки</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>1335169</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>«роторная воздуходувка» G18.3; «купить роторную воздуходувку» G5.2; «воздуходувка роторная цена» G10.6</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>резерв</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>служебная</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>https://cmprg.ru/service</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>cmprg.ru</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>резерв</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/tsentrobezhnye-kompressory</t>
+          <t>https://enger-air.ru/catalog/rotornye-vozdukhoduvki</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1878,7 +1843,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Воздуходувки</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1889,166 +1854,149 @@
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O22" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>«роторная воздуходувка» G18.3; «купить роторную воздуходувку» G5.2; «воздуходувка роторная цена» G10.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>резерв</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>служебная</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://cmprg.ru/service</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>cmprg.ru</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>22</v>
+      </c>
+      <c r="O23" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/tsentrobezhnye-kompressory</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Безмасляные/центробежные</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1335169</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>3</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>14.4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>2</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N24" t="n">
         <v>7.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O24" t="n">
         <v>15.9</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P24" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>«центробежные компрессоры» G7.8; «центробежные компрессоры цена» G7.3; «центробежные компрессоры купить» G3.8</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/vintovye_1</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Безмасляные/центробежные</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>8567838</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>«безмасляный винтовой компрессор» G10.1; «винтовые безмасляные компрессоры купить» G12.6; «безмасляный винтовой компрессор купить» G9.1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/membrannie</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Азотные станции</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>2451874</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>«мембранные генераторы азота» G3.6; «промышленный генератор азота» G9.1; «генераторы азота» G8.8</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vysokogo-davleniya</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/vintovye_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2058,115 +2006,107 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Дожимные/ВД</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5896106</v>
+        <v>8567838</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>битрикс-катег.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="L25" t="n">
-        <v>14.8</v>
+        <v>10.6</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="O25" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="P25" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>«компрессор высокого давления» Я13.3; «промышленный компрессор высокого давления» G8.7; «электрический компрессор высокого давления» G3.5</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+          <t>«безмасляный винтовой компрессор» G10.1; «винтовые безмасляные компрессоры купить» G12.6; «безмасляный винтовой компрессор купить» G9.1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota/generator_azota_kolonnogo_tipa</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/membrannie</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>enger-air.ru</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Азотные станции</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G26" t="n">
         <v>2451874</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>битрикс-бренд+кат.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="n">
+      <c r="J26" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
         <v>12.3</v>
       </c>
-      <c r="M26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>«азотная установка rdrus.ru» Я7.4; «азотная станция принцип работы» G5.5; «азотная установка принцип работы» G11.1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="P26" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>«мембранные генераторы азота» G3.6; «промышленный генератор азота» G9.1; «генераторы азота» G8.8</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/tekhnicheskoe-obsluzhivanie-kompressora</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vysokogo-davleniya</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2176,111 +2116,107 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дожимные/ВД</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>808032</v>
+        <v>5896106</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>35</v>
+      </c>
       <c r="L27" t="n">
-        <v>8.199999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="M27" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>13.5</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
-        <v>10.9</v>
+        <v>13.1</v>
       </c>
       <c r="P27" t="n">
-        <v>10.9</v>
+        <v>13.1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>«то компрессоров» Я7.8; «обслуживание компрессора воздушного» Я8.9; «обслуживание компрессоров» Я8.7</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+          <t>«компрессор высокого давления» Я13.3; «промышленный компрессор высокого давления» G8.7; «электрический компрессор высокого давления» G3.5</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/generatsiya-gazov/generatory-kisloroda</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Кислородные станции</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota/generator_azota_kolonnogo_tipa</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Азотные станции</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>2451874</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K28" s="2" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>«генератор кислорода промышленный» G15.5; «генератор кислорода для лазерной резки» G4.9</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>12</v>
+      </c>
+      <c r="P28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>«азотная установка rdrus.ru» Я7.4; «азотная станция принцип работы» G5.5; «азотная установка принцип работы» G11.1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/dalgakiran</t>
+          <t>https://prokompressor.ru/services/uslugi/tekhnicheskoe-obsluzhivanie-kompressora</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2301,42 +2237,42 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
+        <v>28.5</v>
+      </c>
       <c r="L29" t="n">
-        <v>12.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N29" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="O29" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="P29" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>«далгакиран компрессор» G5.9; «компрессор винтовой далгакиран» G4.7; «поршневые компрессоры dalgakiran» G3.9</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
+          <t>«то компрессоров» Я7.8; «обслуживание компрессора воздушного» Я8.9; «обслуживание компрессоров» Я8.7</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/atlas-copco</t>
+          <t>https://prokompressor.ru/catalog/generatsiya-gazov/generatory-kisloroda</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2346,687 +2282,631 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Кислородные станции</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>808032</v>
+        <v>2451874</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
       <c r="J30" t="n">
-        <v>4.3</v>
+        <v>15.6</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
-      </c>
-      <c r="L30" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>13.1</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="P30" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>«винтовой компрессор atlas copco» Я9.7; «компрессор atlas copco» Я10.1; «атлас копко компрессор» G7.8</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
+          <t>«генератор кислорода промышленный» G15.5; «генератор кислорода для лазерной резки» G4.9</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/dalgakiran</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>«далгакиран компрессор» G5.9; «компрессор винтовой далгакиран» G4.7; «поршневые компрессоры dalgakiran» G3.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/atlas-copco</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>21</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M32" t="n">
+        <v>8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>«винтовой компрессор atlas copco» Я9.7; «компрессор atlas copco» Я10.1; «атлас копко компрессор» G7.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>https://enger-air.ru/catalog/kompressory-nizkogo-davleniya</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>enger-air.ru</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="G33" t="n">
         <v>1335169</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
+      <c r="J33" t="n">
         <v>7.6</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K33" t="n">
         <v>3</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L33" t="n">
         <v>10.9</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N33" t="n">
         <v>5.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O33" t="n">
         <v>10.3</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P33" t="n">
         <v>6.9</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>«компрессор низкого давления» Я12.6; «компрессоры. низкого. давления. воздуходувки.» G4.5; «компрессоры низкого давления» Я9.5</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://enger-air.ru/manuals</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>enger-air.ru</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G34" t="n">
         <v>1335169</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="n">
+      <c r="L34" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="M34" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N34" t="n">
         <v>5.1</v>
       </c>
-      <c r="O32" s="2" t="n">
+      <c r="O34" t="n">
         <v>10.3</v>
       </c>
-      <c r="P32" s="2" t="n">
+      <c r="P34" t="n">
         <v>6.9</v>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/porshnevye</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Безмасляные/центробежные</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>8567838</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>«поршневой безмасляный компрессор купить» G6.7; «купить безмасляный поршневой компрессор» G12.7; «поршневой безмасляный компрессор» G6.4</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>фасет-дубль</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1000-l-min</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор 1000 л мин» G8.3; «компрессор 1000 л/мин» G4.8; «компрессор 1000 л мин купить» G5.0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/porshnevye</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Безмасляные/центробежные</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>8567838</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10</v>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>«поршневой безмасляный компрессор купить» G6.7; «купить безмасляный поршневой компрессор» G12.7; «поршневой безмасляный компрессор» G6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1000-l-min</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>«компрессор 1000 л мин» G8.3; «компрессор 1000 л/мин» G4.8; «компрессор 1000 л мин купить» G5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-kompressora</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Винтовые</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="G37" t="n">
         <v>808032</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="L37" t="n">
         <v>10</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M37" t="n">
         <v>6</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N37" t="n">
         <v>10.8</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O37" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P37" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>«винтовой компрессор ремонт» Я10.0; «винтовой компрессор ремонт promcomtech.ru/remont-vintovykh-kompressorov/» Я10.9; «ремонт винтовых компрессоров» Я8.3</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>https://berg-compressor.com/catalog/vintovye-kompressory</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>berg-compressor.com</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Винтовые</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>1557410</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>«купить винтовой компрессор» G15.6; «винтовой компрессор купить» G14.6; «винтовые компрессоры официальный сайт» G6.2</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/elektricheskie_1</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Винтовые</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>1523189</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор винтовой воздушный электрический» G14.0; «компрессоры винтовые электрические» G13.5; «компрессор воздушный винтовой электрический» G10.8</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog</t>
+          <t>https://berg-compressor.com/catalog/vintovye-kompressory</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>berg-compressor.com</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>808032</v>
+        <v>1557410</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
       <c r="J38" t="n">
-        <v>21.7</v>
+        <v>18.8</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
       </c>
-      <c r="L38" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5</v>
-      </c>
       <c r="N38" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="O38" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="P38" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>«компрессор центр барнаул» G7.4; «каталог компрессоров» G17.2</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+          <t>«купить винтовой компрессор» G15.6; «винтовой компрессор купить» G14.6; «винтовые компрессоры официальный сайт» G6.2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-085ha</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/elektricheskie_1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1004759</v>
+        <v>1523189</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
       <c r="L39" t="n">
-        <v>10.6</v>
+        <v>9.9</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>4.9</v>
       </c>
       <c r="O39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>«компрессор винтовой воздушный электрический» G14.0; «компрессоры винтовые электрические» G13.5; «компрессор воздушный винтовой электрический» G10.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O40" t="n">
         <v>7.4</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>«компрессор центр барнаул» G7.4; «каталог компрессоров» G17.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-085ha</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Осушители</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1004759</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" t="n">
         <v>4.9</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="O41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>«рефрижераторный осушитель» Я11.3; «рефрижераторный осушитель воздуха» Я9.7</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>фасет-дубль</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-5000-l-min</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O40" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор 5000 л мин» G8.4; «винтовой компрессор 5000 л мин» Я9.8; «компрессор 5 м3 мин» G8.6</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>1335169</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O41" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-5000-l-min</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3047,218 +2927,194 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N42" t="n">
+        <v>9</v>
+      </c>
+      <c r="O42" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>«компрессор 5000 л мин» G8.4; «винтовой компрессор 5000 л мин» Я9.8; «компрессор 5 м3 мин» G8.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1335169</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
         <v>35.1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
+      <c r="L44" t="n">
         <v>20.6</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M44" t="n">
         <v>4</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N44" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O44" t="n">
         <v>7.1</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P44" t="n">
         <v>7.1</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>«компрессор» G14.2; «винтовой компрессор 400 литров в минуту» Я10.1; «компрессорное оборудование купить» Я10.2</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="2" t="inlineStr">
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://dali-kompressor.ru/catalog/ca</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>dali-kompressor.ru</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G45" t="n">
         <v>4462526</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="J45" t="n">
         <v>7.9</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K45" t="n">
         <v>1</v>
       </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="n">
+      <c r="N45" t="n">
         <v>1.2</v>
       </c>
-      <c r="O43" s="2" t="n">
+      <c r="O45" t="n">
         <v>6.5</v>
       </c>
-      <c r="P43" s="2" t="n">
+      <c r="P45" t="n">
         <v>5.2</v>
       </c>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>«винтовой компрессор cross air» G8.0; «винтовой компрессор кросс аир» G6.4; «кросс аир компрессор» G6.6</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>фасет-дубль</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-500-l-min</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор 500 литров в минуту» G8.6; «компрессор 500л» G11.2; «компрессор 500 л мин цена» G10.7</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>https://ac-kompressor.ru/catalog/dizelnye-kompressory-do-8-bar/dizelnyy-kompressor-atlas-copco-xas-48-kd-</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>ac-kompressor.ru</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Дизельные/передвижные</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>2355138</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>«дизельные компрессоры атлас» Я9.1; «компрессор дизельный атлас копко» Я8.8</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-lazernoy-rezki</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-500-l-min</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3279,217 +3135,199 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="K46" t="n">
-        <v>3</v>
+        <v>12.2</v>
       </c>
       <c r="L46" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="M46" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M46" t="n">
+        <v>5</v>
+      </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="O46" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="P46" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>«компрессор для лазерной резки металла» G9.5; «винтовой компрессор для лазерного станка» G10.8; «компрессор для лазерного гравера» G8.9</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
+          <t>«компрессор 500 литров в минуту» G8.6; «компрессор 500л» G11.2; «компрессор 500 л мин цена» G10.7</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>https://ac-kompressor.ru/catalog/dizelnye-kompressory-do-8-bar/dizelnyy-kompressor-atlas-copco-xas-48-kd-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ac-kompressor.ru</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Дизельные/передвижные</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2355138</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>«дизельные компрессоры атлас» Я9.1; «компрессор дизельный атлас копко» Я8.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-lazernoy-rezki</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="N48" t="n">
+        <v>7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>«компрессор для лазерной резки металла» G9.5; «винтовой компрессор для лазерного станка» G10.8; «компрессор для лазерного гравера» G8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-300-bar</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="G49" t="n">
         <v>774697</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>payload</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
+      <c r="J49" t="n">
         <v>11.7</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K49" t="n">
         <v>3</v>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="n">
+      <c r="N49" t="n">
         <v>7</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O49" t="n">
         <v>5.4</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P49" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>«компрессор высокого давления 300 бар» G8.6; «компрессор высокого давления 300 атм купить» G8.5; «компрессор 300 бар» G7.6</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>https://zif-kompressor.ru/catalog/vzryvozashchishchennye-kompressory</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>zif-kompressor.ru</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>3050183</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>«взрывозащищенные компрессоры» Я8.4</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-205ha</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Осушители</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>1004759</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>«осушитель воздуха с охлаждением» Я7.8</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://abac-kompressor.ru/catalog/spinn-mini</t>
+          <t>https://zif-kompressor.ru/catalog/vzryvozashchishchennye-kompressory</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>abac-kompressor.ru</t>
+          <t>zif-kompressor.ru</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3498,108 +3336,99 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>808032</v>
+        <v>3050183</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
       <c r="L50" t="n">
-        <v>7.7</v>
+        <v>11.2</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="O50" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P50" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>«винтовой мини компрессор» Я7.5; «компрессор миниатюрный винтовой» Я7.7</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
+          <t>«взрывозащищенные компрессоры» Я8.4</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga-11</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-205ha</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>808032</v>
+        <v>1004759</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
       <c r="L51" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="O51" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P51" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>«компрессор atlas copco ga11ff» Я6.9</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
+          <t>«осушитель воздуха с охлаждением» Я7.8</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga-37</t>
+          <t>https://abac-kompressor.ru/catalog/spinn-mini</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>abac-kompressor.ru</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3615,11 +3444,11 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>34.5</v>
+      </c>
       <c r="L52" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="M52" t="n">
         <v>4</v>
@@ -3635,83 +3464,70 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 37 квт» Я6.4</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
+          <t>«винтовой мини компрессор» Я7.5; «компрессор миниатюрный винтовой» Я7.7</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="inlineStr"/>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-peredvizhnye</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://ac-kompressor.ru/catalog/ga-11</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>ac-kompressor.ru</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Дизельные/передвижные</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>2355138</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O53" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор дизельный передвижной атлас копко» Я10.6; «дизельные компрессоры atlas copco купить» Я11.6</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>«компрессор atlas copco ga11ff» Я6.9</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/bustery</t>
+          <t>https://ac-kompressor.ru/catalog/ga-37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3727,44 +3543,39 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4</v>
+      </c>
+      <c r="N54" t="n">
         <v>6</v>
       </c>
-      <c r="L54" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3</v>
-      </c>
-      <c r="N54" t="n">
-        <v>4.9</v>
-      </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>«дожимной компрессор» G10.9; «компрессор» Я17.5</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
+          <t>«винтовой компрессор 37 квт» Я6.4</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-ga</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-peredvizhnye</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3774,53 +3585,45 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>808032</v>
+        <v>2355138</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P55" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>«компрессор atlas copco» Я11.7; «компрессор atlas copco ga» Я8.5; «atlas copco компрессор» Я11.3</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+          <t>«компрессор дизельный передвижной атлас копко» Я10.6; «дизельные компрессоры atlas copco купить» Я11.6</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/rkz</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/bustery</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3841,11 +3644,14 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K56" t="n">
+        <v>6</v>
+      </c>
       <c r="L56" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="M56" t="n">
         <v>3</v>
@@ -3861,82 +3667,68 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>«ркз компрессор официальный сайт» Я7.5; «ркз компрессор» Я9.8</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+          <t>«дожимной компрессор» G10.9; «компрессор» Я17.5</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="inlineStr"/>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>фасет-дубль</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1500-l-min</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://ac-kompressor.ru/catalog/kompressory-ga</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ac-kompressor.ru</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" t="n">
         <v>808032</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L57" s="2" t="n">
+      <c r="J57" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="L57" t="n">
         <v>10.6</v>
       </c>
-      <c r="M57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор винтовой 1500 л мин» Я10.6; «компрессор 1500 л мин» G13.0; «компрессор 1500 л мин цена» G10.4</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>«компрессор atlas copco» Я11.7; «компрессор atlas copco ga» Я8.5; «atlas copco компрессор» Я11.3</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12-bar</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/rkz</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3957,167 +3749,157 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4</v>
+      </c>
+      <c r="P58" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>«ркз компрессор официальный сайт» Я7.5; «ркз компрессор» Я9.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1500-l-min</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>«компрессор винтовой 1500 л мин» Я10.6; «компрессор 1500 л мин» G13.0; «компрессор 1500 л мин цена» G10.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12-bar</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
         <v>6.3</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K60" t="n">
         <v>3</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L60" t="n">
         <v>24.8</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M60" t="n">
         <v>2</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N60" t="n">
         <v>4.4</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O60" t="n">
         <v>3.6</v>
       </c>
-      <c r="P58" t="n">
+      <c r="P60" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>«компрессор воздушный 12 атмосфер» G8.7; «компрессоры 12 атмосфер» G5.4; «компрессоры 12 квт» G3.8</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-tsekha</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O59" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор промышленный» G17.4; «компрессор воздушный промышленный» G17.9; «компрессор промышленный купить» G15.7</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/elektricheskie-kompressory</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Дизельные/передвижные</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>1335169</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>«цена передвижные компрессоры» Я10.7; «купить передвижные компрессоры» Я10.9</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga55</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-tsekha</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4133,17 +3915,17 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>18</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2</v>
+      </c>
       <c r="L61" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M61" t="n">
-        <v>3</v>
+        <v>34.3</v>
       </c>
       <c r="N61" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O61" t="n">
         <v>3.6</v>
@@ -4153,2044 +3935,1978 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 55 квт» Я6.7</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
+          <t>«компрессор промышленный» G17.4; «компрессор воздушный промышленный» G17.9; «компрессор промышленный купить» G15.7</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/xas</t>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/elektricheskie-kompressory</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>808032</v>
+        <v>1335169</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
       <c r="L62" t="n">
-        <v>9.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="O62" t="n">
         <v>3.6</v>
       </c>
       <c r="P62" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>«дизельный компрессор atlas copco» Я9.8; «дизельные компрессоры xas» Я8.7; «дизельный компрессор atlas» Я8.4</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
+          <t>«цена передвижные компрессоры» Я10.7; «купить передвижные компрессоры» Я10.9</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/osushiteli</t>
+          <t>https://ac-kompressor.ru/catalog/ga55</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>792758</v>
+        <v>808032</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K63" t="n">
-        <v>64</v>
+          <t>прайс-сегмент</t>
+        </is>
       </c>
       <c r="L63" t="n">
-        <v>21.7</v>
+        <v>9.4</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P63" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>«осушитель сжатого воздуха для компрессора» G9.6; «осушитель сжатого воздуха» G17.5; «осушитель для компрессора цена» G4.8</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
+          <t>«винтовой компрессор 55 квт» Я6.7</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://remeza-kompressor.ru/catalog/modulnye-kompressornye-stantsii</t>
+          <t>https://ac-kompressor.ru/catalog/xas</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>remeza-kompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Модульные/блочные КС</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>741144</v>
+        <v>808032</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
       <c r="L64" t="n">
-        <v>15.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M64" t="n">
         <v>3</v>
       </c>
       <c r="N64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P64" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>«дизельный компрессор atlas copco» Я9.8; «дизельные компрессоры xas» Я8.7; «дизельный компрессор atlas» Я8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/catalog/osushiteli</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>prokompressor.ru</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Осушители</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>792758</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>64</v>
+      </c>
+      <c r="L65" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>«осушитель сжатого воздуха для компрессора» G9.6; «осушитель сжатого воздуха» G17.5; «осушитель для компрессора цена» G4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://remeza-kompressor.ru/catalog/modulnye-kompressornye-stantsii</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>remeza-kompressor.ru</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Модульные/блочные КС</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>741144</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3</v>
+      </c>
+      <c r="N66" t="n">
         <v>4.8</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O66" t="n">
         <v>3.5</v>
       </c>
-      <c r="P64" t="n">
+      <c r="P66" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>«модульная компрессорная станция» Я10.7</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" s="2" t="inlineStr">
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>https://crossair-compressor.ru/catalog/vintovye-kompressory</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>crossair-compressor.ru</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Винтовые</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G67" t="n">
         <v>838752</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="n">
+      <c r="L67" t="n">
         <v>11.6</v>
       </c>
-      <c r="M65" s="2" t="n">
+      <c r="M67" t="n">
         <v>2</v>
       </c>
-      <c r="N65" s="2" t="n">
+      <c r="N67" t="n">
         <v>3.3</v>
       </c>
-      <c r="O65" s="2" t="n">
+      <c r="O67" t="n">
         <v>3.4</v>
       </c>
-      <c r="P65" s="2" t="n">
+      <c r="P67" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q65" s="2" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>«винтовой компрессор cross air» Я10.5; «винтовой компрессор кросс аир» Я10.2; «cross air компрессор винтовой» Я10.4</t>
         </is>
       </c>
-      <c r="R65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="2" t="inlineStr">
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/osushiteli/refrizheratornye</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Осушители</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G68" t="n">
         <v>792758</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>битрикс-катег.</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="n">
+      <c r="J68" t="n">
         <v>14.5</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="K68" t="n">
         <v>1</v>
       </c>
-      <c r="L66" s="2" t="n">
+      <c r="L68" t="n">
         <v>26.7</v>
       </c>
-      <c r="M66" s="2" t="n">
+      <c r="M68" t="n">
         <v>1</v>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="N68" t="n">
         <v>4.3</v>
       </c>
-      <c r="O66" s="2" t="n">
+      <c r="O68" t="n">
         <v>3.4</v>
       </c>
-      <c r="P66" s="2" t="n">
+      <c r="P68" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q66" s="2" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>«рефрижераторный осушитель воздуха» G18.8; «рефрижераторный осушитель сжатого воздуха» G18.8; «осушитель рефрижераторного типа купить» G10.5</t>
         </is>
       </c>
-      <c r="R66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr"/>
-      <c r="C67" s="2" t="inlineStr">
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="C69" t="inlineStr">
         <is>
           <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/5000-to-5000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Винтовые</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G69" t="n">
         <v>1523189</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>битрикс-катег.</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="n">
+      <c r="L69" t="n">
         <v>13.6</v>
       </c>
-      <c r="M67" s="2" t="n">
+      <c r="M69" t="n">
         <v>1</v>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="N69" t="n">
         <v>2.2</v>
       </c>
-      <c r="O67" s="2" t="n">
+      <c r="O69" t="n">
         <v>3.4</v>
       </c>
-      <c r="P67" s="2" t="n">
+      <c r="P69" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q67" s="2" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>«винтовой компрессор 5000 л мин» Я15.3; «винтовой компрессор 5000 л мин цена» Я8.3</t>
         </is>
       </c>
-      <c r="R67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Осушители</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>1004759</v>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>«осушители воздуха аирфловер» Я10.6</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr"/>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Дизельные/передвижные</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>1335169</v>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O69" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>«компрессор воздушный передвижной» Я11.8; «компрессор воздушный дизельный» Я10.6; «компрессор мобильный дизельный» Я11.6</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Осушители</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1004759</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>«осушители воздуха аирфловер» Я10.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Дизельные/передвижные</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1335169</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O71" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>«компрессор воздушный передвижной» Я11.8; «компрессор воздушный дизельный» Я10.6; «компрессор мобильный дизельный» Я11.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>https://prokompressor.ru/catalog/resivery</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Ресиверы</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="G72" t="n">
         <v>113458</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>битрикс-катег.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="n">
+      <c r="J72" t="n">
         <v>12.5</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K72" t="n">
         <v>12</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L72" t="n">
         <v>33.4</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M72" t="n">
         <v>2</v>
       </c>
-      <c r="N70" t="n">
+      <c r="N72" t="n">
         <v>28</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O72" t="n">
         <v>3.2</v>
       </c>
-      <c r="P70" t="n">
+      <c r="P72" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>«ресивер для компрессора» G14.7; «воздушный ресивер» G16.0; «купить ресивер для воздуха» G4.2</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" s="2" t="inlineStr">
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="C73" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G73" t="n">
         <v>808032</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="n">
+      <c r="L73" t="n">
         <v>18.7</v>
       </c>
-      <c r="M71" s="2" t="n">
+      <c r="M73" t="n">
         <v>1</v>
       </c>
-      <c r="N71" s="2" t="n">
+      <c r="N73" t="n">
         <v>3.7</v>
       </c>
-      <c r="O71" s="2" t="n">
+      <c r="O73" t="n">
         <v>3</v>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="P73" t="n">
         <v>3</v>
       </c>
-      <c r="Q71" s="2" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>«компрессоры для производства» Я17.2</t>
         </is>
       </c>
-      <c r="R71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr">
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-moshchnosti/11-kvt</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G74" t="n">
         <v>808032</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="n">
+      <c r="L74" t="n">
         <v>17.1</v>
       </c>
-      <c r="M72" s="2" t="n">
+      <c r="M74" t="n">
         <v>1</v>
       </c>
-      <c r="N72" s="2" t="n">
+      <c r="N74" t="n">
         <v>3.7</v>
       </c>
-      <c r="O72" s="2" t="n">
+      <c r="O74" t="n">
         <v>3</v>
       </c>
-      <c r="P72" s="2" t="n">
+      <c r="P74" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" s="2" t="inlineStr">
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-peskostruya/soplo-8-mm</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G75" t="n">
         <v>808032</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="n">
+      <c r="L75" t="n">
         <v>16.9</v>
       </c>
-      <c r="M73" s="2" t="n">
+      <c r="M75" t="n">
         <v>1</v>
       </c>
-      <c r="N73" s="2" t="n">
+      <c r="N75" t="n">
         <v>3.7</v>
       </c>
-      <c r="O73" s="2" t="n">
+      <c r="O75" t="n">
         <v>3</v>
       </c>
-      <c r="P73" s="2" t="n">
+      <c r="P75" t="n">
         <v>3</v>
       </c>
-      <c r="Q73" s="2" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>«компрессор для пескоструя» Я16.1; «компрессор винтовой для пескоструя» Я17.6</t>
         </is>
       </c>
-      <c r="R73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="2" t="inlineStr">
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>https://remeza-kompressor.ru/catalog/kompressory</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>remeza-kompressor.ru</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G76" t="n">
         <v>741144</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="n">
+      <c r="L76" t="n">
         <v>17.5</v>
       </c>
-      <c r="M74" s="2" t="n">
+      <c r="M76" t="n">
         <v>1</v>
       </c>
-      <c r="N74" s="2" t="n">
+      <c r="N76" t="n">
         <v>3.7</v>
       </c>
-      <c r="O74" s="2" t="n">
+      <c r="O76" t="n">
         <v>2.7</v>
       </c>
-      <c r="P74" s="2" t="n">
+      <c r="P76" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q74" s="2" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>«компрессоры воздушные ремезов» Я12.5</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" s="2" t="inlineStr">
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>https://berg-compressor.com/catalog/kompressory-na-resivere</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>berg-compressor.com</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Ресиверы</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G77" t="n">
         <v>449403</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="n">
+      <c r="J77" t="n">
         <v>26.5</v>
       </c>
-      <c r="K75" s="2" t="n">
+      <c r="K77" t="n">
         <v>1</v>
       </c>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="n">
+      <c r="N77" t="n">
         <v>4.6</v>
       </c>
-      <c r="O75" s="2" t="n">
+      <c r="O77" t="n">
         <v>2.6</v>
       </c>
-      <c r="P75" s="2" t="n">
+      <c r="P77" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q75" s="2" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>«винтовой компрессор на ресивере» G15.4</t>
         </is>
       </c>
-      <c r="R75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr">
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>https://ac-kompressor.ru/catalog/kompressory-zr</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>ac-kompressor.ru</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G78" t="n">
         <v>808032</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="n">
+      <c r="L78" t="n">
         <v>12.3</v>
       </c>
-      <c r="M76" s="2" t="n">
+      <c r="M78" t="n">
         <v>2</v>
       </c>
-      <c r="N76" s="2" t="n">
+      <c r="N78" t="n">
         <v>3.3</v>
       </c>
-      <c r="O76" s="2" t="n">
+      <c r="O78" t="n">
         <v>2.6</v>
       </c>
-      <c r="P76" s="2" t="n">
+      <c r="P78" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr">
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="C79" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>https://ac-kompressor.ru/catalog/vintovye-kompressory</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>ac-kompressor.ru</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Винтовые</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G79" t="n">
         <v>808032</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="n">
+      <c r="J79" t="n">
         <v>34</v>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="n">
+      <c r="L79" t="n">
         <v>11.3</v>
       </c>
-      <c r="M77" s="2" t="n">
+      <c r="M79" t="n">
         <v>2</v>
       </c>
-      <c r="N77" s="2" t="n">
+      <c r="N79" t="n">
         <v>3.3</v>
       </c>
-      <c r="O77" s="2" t="n">
+      <c r="O79" t="n">
         <v>2.6</v>
       </c>
-      <c r="P77" s="2" t="n">
+      <c r="P79" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q77" s="2" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>«винтовой компрессор atlas copco» Я11.7; «купить винтовой компрессор атлас копко» Я11.3; «винтовой компрессор атлас копко» Я10.6</t>
         </is>
       </c>
-      <c r="R77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr">
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/osushiteli_vozdukha/adsorbtsionnye_osushiteli/goryachaya_regeneratsiya/kolonnyy_tip_raskhod_vozdukha_na_regeneratsiyu_4_6/ADH-038L</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>enger-air.ru</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Осушители адсорбц.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G80" t="n">
         <v>1004759</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>битрикс-бренд+кат.</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="n">
+      <c r="L80" t="n">
         <v>12.1</v>
       </c>
-      <c r="M78" s="2" t="n">
+      <c r="M80" t="n">
         <v>1</v>
       </c>
-      <c r="N78" s="2" t="n">
+      <c r="N80" t="n">
         <v>1.6</v>
       </c>
-      <c r="O78" s="2" t="n">
+      <c r="O80" t="n">
         <v>2.5</v>
       </c>
-      <c r="P78" s="2" t="n">
+      <c r="P80" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q78" s="2" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>«адсорбционный осушитель» Я16.5</t>
         </is>
       </c>
-      <c r="R78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" s="2" t="inlineStr">
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/atlas-copco</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Винтовые</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G81" t="n">
         <v>1523189</v>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>битрикс-катег.</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="n">
+      <c r="L81" t="n">
         <v>11.6</v>
       </c>
-      <c r="M79" s="2" t="n">
+      <c r="M81" t="n">
         <v>1</v>
       </c>
-      <c r="N79" s="2" t="n">
+      <c r="N81" t="n">
         <v>1.6</v>
       </c>
-      <c r="O79" s="2" t="n">
+      <c r="O81" t="n">
         <v>2.5</v>
       </c>
-      <c r="P79" s="2" t="n">
+      <c r="P81" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q79" s="2" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>«винтовой компрессор atlas» Я10.1; «винтовой компрессор atlas copco авито» Я10.5; «купить винтовой компрессор атлас копко» Я10.9</t>
         </is>
       </c>
-      <c r="R79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr">
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>https://berg-compressor.com/catalog/refrizheratornye-osushiteli</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>berg-compressor.com</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Осушители</t>
         </is>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G82" t="n">
         <v>442250</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>битрикс-бренд+кат.</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="n">
+      <c r="J82" t="n">
         <v>13.7</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="K82" t="n">
         <v>2</v>
       </c>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="n">
+      <c r="N82" t="n">
         <v>4.3</v>
       </c>
-      <c r="O80" s="2" t="n">
+      <c r="O82" t="n">
         <v>2.4</v>
       </c>
-      <c r="P80" s="2" t="n">
+      <c r="P82" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q80" s="2" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>«рефрижераторный осушитель» G15.6; «осушитель рефрижераторный» G9.2; «рефрижераторный осушитель воздуха» G11.4</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr"/>
-      <c r="C81" s="2" t="inlineStr">
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="C83" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/kompressory-40-bar</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>enger-air.ru</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G83" t="n">
         <v>1335169</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="n">
+      <c r="J83" t="n">
         <v>9.5</v>
       </c>
-      <c r="K81" s="2" t="n">
+      <c r="K83" t="n">
         <v>1</v>
       </c>
-      <c r="L81" s="2" t="n">
+      <c r="L83" t="n">
         <v>14</v>
       </c>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="n">
+      <c r="N83" t="n">
         <v>1.2</v>
       </c>
-      <c r="O81" s="2" t="n">
+      <c r="O83" t="n">
         <v>2.3</v>
       </c>
-      <c r="P81" s="2" t="n">
+      <c r="P83" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q81" s="2" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>«винтовой компрессор 40 бар» G11.1; «дожимной компрессор высокого давления» G7.5; «дожимной компрессор 40 бар» G3.9</t>
         </is>
       </c>
-      <c r="R81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="2" t="inlineStr">
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>https://enger-air.ru/catalog/vintovye_kompressory/lazer</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>enger-air.ru</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Винтовые</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G84" t="n">
         <v>1335169</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="n">
+      <c r="J84" t="n">
         <v>7.9</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="K84" t="n">
         <v>1</v>
       </c>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="n">
+      <c r="N84" t="n">
         <v>1.2</v>
       </c>
-      <c r="O82" s="2" t="n">
+      <c r="O84" t="n">
         <v>2.3</v>
       </c>
-      <c r="P82" s="2" t="n">
+      <c r="P84" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q82" s="2" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>«винтовой компрессор для лазерной резки» G5.2</t>
         </is>
       </c>
-      <c r="R82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr"/>
-      <c r="C83" s="2" t="inlineStr">
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" t="inlineStr">
         <is>
           <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12000-l-min</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G85" t="n">
         <v>808032</v>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="n">
+      <c r="J85" t="n">
         <v>15.2</v>
       </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="n">
+      <c r="L85" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M83" s="2" t="n">
+      <c r="M85" t="n">
         <v>1</v>
       </c>
-      <c r="N83" s="2" t="n">
+      <c r="N85" t="n">
         <v>2.6</v>
       </c>
-      <c r="O83" s="2" t="n">
+      <c r="O85" t="n">
         <v>2.1</v>
       </c>
-      <c r="P83" s="2" t="n">
+      <c r="P85" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q83" s="2" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>«компрессор 12000 л/мин» G5.2; «компрессоры 12000 л/мин» G3.7; «компрессор 75 квт» G11.1</t>
         </is>
       </c>
-      <c r="R83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="2" t="inlineStr">
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-bloka</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Винтовые</t>
         </is>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="G86" t="n">
         <v>808032</v>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="n">
+      <c r="J86" t="n">
         <v>8.9</v>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="n">
+      <c r="L86" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M84" s="2" t="n">
+      <c r="M86" t="n">
         <v>1</v>
       </c>
-      <c r="N84" s="2" t="n">
+      <c r="N86" t="n">
         <v>2.6</v>
       </c>
-      <c r="O84" s="2" t="n">
+      <c r="O86" t="n">
         <v>2.1</v>
       </c>
-      <c r="P84" s="2" t="n">
+      <c r="P86" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q84" s="2" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>«ремонт винтового компрессора» G11.1; «ремонт винтового блока компрессора» Я9.0; «ремонт винтовых блоков» Я10.1</t>
         </is>
       </c>
-      <c r="R84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="2" t="inlineStr">
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15000-l-min</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="G87" t="n">
         <v>808032</v>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="n">
+      <c r="J87" t="n">
         <v>11.2</v>
       </c>
-      <c r="K85" s="2" t="n">
+      <c r="K87" t="n">
         <v>1</v>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L87" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="n">
+      <c r="N87" t="n">
         <v>2.3</v>
       </c>
-      <c r="O85" s="2" t="n">
+      <c r="O87" t="n">
         <v>1.9</v>
       </c>
-      <c r="P85" s="2" t="n">
+      <c r="P87" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q85" s="2" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>«компрессор 15 бар» G10.3; «винтовой компрессор 15 м3 мин» Я7.9; «купить компрессор 15 атмосфер» G9.6</t>
         </is>
       </c>
-      <c r="R85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="2" t="inlineStr">
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-20-bar</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="G88" t="n">
         <v>808032</v>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="n">
+      <c r="J88" t="n">
         <v>10.9</v>
       </c>
-      <c r="K86" s="2" t="n">
+      <c r="K88" t="n">
         <v>1</v>
       </c>
-      <c r="L86" s="2" t="n">
+      <c r="L88" t="n">
         <v>18.3</v>
       </c>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="n">
+      <c r="N88" t="n">
         <v>2.3</v>
       </c>
-      <c r="O86" s="2" t="n">
+      <c r="O88" t="n">
         <v>1.9</v>
       </c>
-      <c r="P86" s="2" t="n">
+      <c r="P88" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q86" s="2" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>«компрессор 20 бар» G11.9; «компрессор 20 бар цена» G8.5; «купить компрессор 20 атмосфер» G8.2</t>
         </is>
       </c>
-      <c r="R86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" s="2" t="inlineStr">
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="C89" t="inlineStr">
         <is>
           <t>кликов 2</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/osushiteli/adsorbtsionnye</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Осушители адсорбц.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="G89" t="n">
         <v>792758</v>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>битрикс-катег.</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="n">
+      <c r="J89" t="n">
         <v>17.3</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="K89" t="n">
         <v>1</v>
       </c>
-      <c r="L87" s="2" t="n">
+      <c r="L89" t="n">
         <v>32.4</v>
       </c>
-      <c r="M87" s="2" t="n">
+      <c r="M89" t="n">
         <v>1</v>
       </c>
-      <c r="N87" s="2" t="n">
+      <c r="N89" t="n">
         <v>2.2</v>
       </c>
-      <c r="O87" s="2" t="n">
+      <c r="O89" t="n">
         <v>1.8</v>
       </c>
-      <c r="P87" s="2" t="n">
+      <c r="P89" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q87" s="2" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>«адсорбционный осушитель» G12.3; «адсорбционный осушитель воздуха» G19.7; «адсорбционный осушитель воздуха купить» G15.6</t>
         </is>
       </c>
-      <c r="R87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr"/>
-      <c r="C88" s="2" t="inlineStr">
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/services/uslugi/montazh</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="G90" t="n">
         <v>808032</v>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="n">
+      <c r="L90" t="n">
         <v>21.3</v>
       </c>
-      <c r="M88" s="2" t="n">
+      <c r="M90" t="n">
         <v>1</v>
       </c>
-      <c r="N88" s="2" t="n">
+      <c r="N90" t="n">
         <v>2.2</v>
       </c>
-      <c r="O88" s="2" t="n">
+      <c r="O90" t="n">
         <v>1.8</v>
       </c>
-      <c r="P88" s="2" t="n">
+      <c r="P90" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q88" s="2" t="inlineStr"/>
-      <c r="R88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr"/>
-      <c r="C89" s="2" t="inlineStr">
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/services/uslugi/remont-osushiteley</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Осушители</t>
         </is>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="G91" t="n">
         <v>493116</v>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="n">
+      <c r="L91" t="n">
         <v>15.6</v>
       </c>
-      <c r="M89" s="2" t="n">
+      <c r="M91" t="n">
         <v>1</v>
       </c>
-      <c r="N89" s="2" t="n">
+      <c r="N91" t="n">
         <v>3.7</v>
       </c>
-      <c r="O89" s="2" t="n">
+      <c r="O91" t="n">
         <v>1.8</v>
       </c>
-      <c r="P89" s="2" t="n">
+      <c r="P91" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q89" s="2" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>«ремонт осушителя воздуха для компрессора» Я14.9</t>
         </is>
       </c>
-      <c r="R89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr">
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/cross-air</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="G92" t="n">
         <v>808032</v>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="n">
+      <c r="J92" t="n">
         <v>13.4</v>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="n">
+      <c r="L92" t="n">
         <v>15.4</v>
       </c>
-      <c r="M90" s="2" t="n">
+      <c r="M92" t="n">
         <v>1</v>
       </c>
-      <c r="N90" s="2" t="n">
+      <c r="N92" t="n">
         <v>1.6</v>
       </c>
-      <c r="O90" s="2" t="n">
+      <c r="O92" t="n">
         <v>1.6</v>
       </c>
-      <c r="P90" s="2" t="n">
+      <c r="P92" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q90" s="2" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>«винтовой компрессор cross air» G14.8; «компрессор cross air» G13.6</t>
         </is>
       </c>
-      <c r="R90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr"/>
-      <c r="C91" s="2" t="inlineStr">
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>служебная; кликов 1</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/services/uslugi</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="G93" t="n">
         <v>808032</v>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="n">
+      <c r="L93" t="n">
         <v>10.4</v>
       </c>
-      <c r="M91" s="2" t="n">
+      <c r="M93" t="n">
         <v>1</v>
       </c>
-      <c r="N91" s="2" t="n">
+      <c r="N93" t="n">
         <v>1.8</v>
       </c>
-      <c r="O91" s="2" t="n">
+      <c r="O93" t="n">
         <v>1.5</v>
       </c>
-      <c r="P91" s="2" t="n">
+      <c r="P93" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q91" s="2" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>«обслуживание компрессора» Я10.2; «компрессор тех центр serviceset» Я4.2; «установка и обслуживание компрессоров» Я5.9</t>
         </is>
       </c>
-      <c r="R91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="2" t="inlineStr">
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/projects/proizvodstvo/cross-air-argus</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="G94" t="n">
         <v>808032</v>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="n">
+      <c r="L94" t="n">
         <v>9.1</v>
       </c>
-      <c r="M92" s="2" t="n">
+      <c r="M94" t="n">
         <v>1</v>
       </c>
-      <c r="N92" s="2" t="n">
+      <c r="N94" t="n">
         <v>1.5</v>
       </c>
-      <c r="O92" s="2" t="n">
+      <c r="O94" t="n">
         <v>1.5</v>
       </c>
-      <c r="P92" s="2" t="n">
+      <c r="P94" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q92" s="2" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>«аргус компрессор» Я10.9</t>
         </is>
       </c>
-      <c r="R92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr"/>
-      <c r="C93" s="2" t="inlineStr">
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="C95" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>https://ac-kompressor.ru/catalog/kompressory-gx</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>ac-kompressor.ru</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="n">
+      <c r="G95" t="n">
         <v>808032</v>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="n">
+      <c r="L95" t="n">
         <v>10.9</v>
       </c>
-      <c r="M93" s="2" t="n">
+      <c r="M95" t="n">
         <v>1</v>
       </c>
-      <c r="N93" s="2" t="n">
+      <c r="N95" t="n">
         <v>1.6</v>
       </c>
-      <c r="O93" s="2" t="n">
+      <c r="O95" t="n">
         <v>1.3</v>
       </c>
-      <c r="P93" s="2" t="n">
+      <c r="P95" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q93" s="2" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>«atlas copco компрессор» Я10.7; «компрессор atlas copco gx11ff» Я10.8</t>
         </is>
       </c>
-      <c r="R93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr"/>
-      <c r="C94" s="2" t="inlineStr">
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>служебная; кликов 1</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>https://ac-kompressor.ru/company/service</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>ac-kompressor.ru</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="n">
+      <c r="G96" t="n">
         <v>808032</v>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="n">
+      <c r="L96" t="n">
         <v>11.5</v>
       </c>
-      <c r="M94" s="2" t="n">
+      <c r="M96" t="n">
         <v>1</v>
       </c>
-      <c r="N94" s="2" t="n">
+      <c r="N96" t="n">
         <v>1.6</v>
       </c>
-      <c r="O94" s="2" t="n">
+      <c r="O96" t="n">
         <v>1.3</v>
       </c>
-      <c r="P94" s="2" t="n">
+      <c r="P96" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q94" s="2" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>«компрессор атлас копко обслуживание» Я7.9</t>
         </is>
       </c>
-      <c r="R94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr"/>
-      <c r="C95" s="2" t="inlineStr">
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>кликов 1</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15-bar</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="n">
+      <c r="G97" t="n">
         <v>808032</v>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="n">
+      <c r="J97" t="n">
         <v>7.6</v>
       </c>
-      <c r="K95" s="2" t="n">
+      <c r="K97" t="n">
         <v>1</v>
       </c>
-      <c r="L95" s="2" t="n">
+      <c r="L97" t="n">
         <v>26.6</v>
       </c>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="n">
+      <c r="N97" t="n">
         <v>1.2</v>
       </c>
-      <c r="O95" s="2" t="n">
+      <c r="O97" t="n">
         <v>0.9</v>
       </c>
-      <c r="P95" s="2" t="n">
+      <c r="P97" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q95" s="2" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>«компрессор 15 бар» G7.6; «винтовой компрессор 15 бар» G8.2; «компрессор воздушный 15 бар» G8.0</t>
         </is>
       </c>
-      <c r="R95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr"/>
-      <c r="C96" s="2" t="inlineStr">
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-3000-l-min</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="n">
+      <c r="G98" t="n">
         <v>808032</v>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="n">
+      <c r="J98" t="n">
         <v>7.8</v>
       </c>
-      <c r="K96" s="2" t="n">
+      <c r="K98" t="n">
         <v>1</v>
       </c>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="n">
+      <c r="N98" t="n">
         <v>1.2</v>
       </c>
-      <c r="O96" s="2" t="n">
+      <c r="O98" t="n">
         <v>0.9</v>
       </c>
-      <c r="P96" s="2" t="n">
+      <c r="P98" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q96" s="2" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>«компрессор 3000 л мин» G7.2; «компрессор 3000 литров в минуту» G6.3; «винтовой компрессор 3000 л мин» G6.8</t>
         </is>
       </c>
-      <c r="R96" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seo-texts/frog/acceptor-top100.xlsx
+++ b/seo-texts/frog/acceptor-top100.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:R96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1088,98 +1088,145 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha/mobilnye-kompressornye-stantsii</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/dizelnye-kompressory</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>enger-air.ru</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Дизельные/передвижные</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1335169</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ок</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>«дизель компрессор» Я10.1; «дизельный передвижной компрессор promcomtech.ru/catalog/dizelnye-kompressory/peredvizhnye/» Я7.1; «компрессор высокого давления дизельный» Я6.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>агент: качать</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ЯДРО</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>служебная</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://prokompressor.ru/services</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>prokompressor.ru</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Модульные/блочные КС</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>2189896</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>прокси: сегмент КС</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>ДОБАВЛЕНО ВЛАДЕЛЬЦЕМ 05.08: замеров нет (страницы не попали в выгрузку Вебмастера) - позиции/клики неизвестны, приоритет назначен вручную</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>ЯДРО</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/kompressornye-stantsii-szhatogo-vozdukha/dozhimnye-stantsii</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Модульные/блочные КС</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>2189896</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>прокси: сегмент КС</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>ДОБАВЛЕНО ВЛАДЕЛЬЦЕМ 05.08: замеров нет (страницы не попали в выгрузку Вебмастера) - позиции/клики неизвестны, приоритет назначен вручную</t>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Бренд/категория (смеш.)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>808032</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>не проверить</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>33</v>
+      </c>
+      <c r="N11" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>«ремонт и обслуживание компрессоров» G10.9; «техническое обслуживание компрессоров теплообменников» Я5.0; «обслуживание винтовых компрессоров» G16.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>агент: качать</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1241,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/dizelnye-kompressory</t>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1204,15 +1251,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Азотные станции</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1335169</v>
+        <v>2451874</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1221,29 +1268,23 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5.3</v>
+        <v>11.4</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>29.4</v>
+        <v>11.7</v>
       </c>
       <c r="O12" t="n">
-        <v>58.9</v>
+        <v>42.9</v>
       </c>
       <c r="P12" t="n">
-        <v>39.3</v>
+        <v>28.6</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>«дизель компрессор» Я10.1; «дизельный передвижной компрессор promcomtech.ru/catalog/dizelnye-kompressory/peredvizhnye/» Я7.1; «компрессор высокого давления дизельный» Я6.7</t>
+          <t>«генератор азота цена» G18.2; «генератор азота» G14.1; «адсорбционный генератор азота» G7.6</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1261,14 +1302,9 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>служебная</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1278,46 +1314,46 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>808032</v>
+        <v>1523189</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>не проверить</t>
+          <t>ок</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>28.2</v>
+        <v>17.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>11.4</v>
+        <v>15.4</v>
       </c>
       <c r="M13" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>58.5</v>
+        <v>25.9</v>
       </c>
       <c r="O13" t="n">
-        <v>47.2</v>
+        <v>39.5</v>
       </c>
       <c r="P13" t="n">
-        <v>47.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>«ремонт и обслуживание компрессоров» G10.9; «техническое обслуживание компрессоров теплообменников» Я5.0; «обслуживание винтовых компрессоров» G16.0</t>
+          <t>«винтовой компрессор» G15.0; «стоимость винтового компрессора» G10.7; «компрессор промышленный винтовой» G15.7</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1337,7 +1373,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1347,11 +1383,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Азотные станции</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2451874</v>
+        <v>1004759</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1360,27 +1396,33 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ок</t>
+          <t>завышен</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>11.7</v>
+        <v>24.4</v>
       </c>
       <c r="O14" t="n">
-        <v>42.9</v>
+        <v>36.7</v>
       </c>
       <c r="P14" t="n">
-        <v>28.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>«генератор азота цена» G18.2; «генератор азота» G14.1; «адсорбционный генератор азота» G7.6</t>
+          <t>«рефрижераторный осушитель воздуха» G6.4; «осушитель рефрижераторного типа» G5.8; «осушитель сжатого воздуха рефрижераторного типа» G5.5</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1400,61 +1442,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye</t>
+          <t>https://enger-air.ru/catalog/mks</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1523189</v>
+        <v>1335169</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ок</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17.9</v>
+        <v>8.6</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
-        <v>15.4</v>
+        <v>10.5</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>25.9</v>
+        <v>15.9</v>
       </c>
       <c r="O15" t="n">
-        <v>39.5</v>
+        <v>31.8</v>
       </c>
       <c r="P15" t="n">
-        <v>39.5</v>
+        <v>21.2</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>«винтовой компрессор» G15.0; «стоимость винтового компрессора» G10.7; «компрессор промышленный винтовой» G15.7</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>агент: качать</t>
+          <t>«модульные компрессорные станции» G6.4; «модульная компрессорная станция мкс» G8.3; «компрессорная» G8.3</t>
         </is>
       </c>
     </row>
@@ -1469,61 +1501,51 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/dizelnye</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1004759</v>
+        <v>2355138</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>завышен</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O16" t="n">
         <v>23.8</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>36.7</v>
-      </c>
       <c r="P16" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>«рефрижераторный осушитель воздуха» G6.4; «осушитель рефрижераторного типа» G5.8; «осушитель сжатого воздуха рефрижераторного типа» G5.5</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>агент: качать</t>
+          <t>«дизельный компрессор» G10.5; «компрессоры винтовые дизельные воздушные» G7.7; «винтовой компрессор на шасси» G11.8</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1560,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/mks</t>
+          <t>https://enger-air.ru/catalog/kislorodnye-ustanovki/generator-kisloroda</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1548,41 +1570,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Кислородные станции</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1335169</v>
+        <v>2451874</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>15.9</v>
+        <v>6.3</v>
       </c>
       <c r="O17" t="n">
-        <v>31.8</v>
+        <v>23.2</v>
       </c>
       <c r="P17" t="n">
-        <v>21.2</v>
+        <v>15.5</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>«модульные компрессорные станции» G6.4; «модульная компрессорная станция мкс» G8.3; «компрессорная» G8.3</t>
+          <t>«генератор кислорода» G10.4; «кислородный генератор» G10.9; «кислородные генераторы» G14.7</t>
         </is>
       </c>
     </row>
@@ -1595,9 +1611,14 @@
           <t>ЯДРО</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/dizelnye</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/kompressory-40-bar</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1607,41 +1628,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2355138</v>
+        <v>12986897</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
+          <t>payload</t>
+        </is>
       </c>
       <c r="L18" t="n">
-        <v>22.1</v>
+        <v>10.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>10.1</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>23.8</v>
+        <v>21.2</v>
       </c>
       <c r="P18" t="n">
-        <v>23.8</v>
+        <v>21.2</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>«дизельный компрессор» G10.5; «компрессоры винтовые дизельные воздушные» G7.7; «винтовой компрессор на шасси» G11.8</t>
+          <t>«винтовой компрессор 40 бар» Я10.7</t>
         </is>
       </c>
     </row>
@@ -1651,50 +1666,58 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ЯДРО</t>
+          <t>резерв</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/kislorodnye-ustanovki/generator-kisloroda</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-bezmaslyanye</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Кислородные станции</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2451874</v>
+        <v>8567838</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>38.1</v>
       </c>
       <c r="N19" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="O19" t="n">
-        <v>23.2</v>
+        <v>18.4</v>
       </c>
       <c r="P19" t="n">
-        <v>15.5</v>
+        <v>18.4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>«генератор кислорода» G10.4; «кислородный генератор» G10.9; «кислородные генераторы» G14.7</t>
+          <t>«безмасляный компрессор купить» G15.6; «безмасляный воздушный компрессор» G18.4; «безмасляный воздушный компрессор купить» G14.9</t>
         </is>
       </c>
     </row>
@@ -1704,55 +1727,58 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ЯДРО</t>
+          <t>резерв</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/kompressory-40-bar</t>
+          <t>https://enger-air.ru/catalog/rotornye-vozdukhoduvki</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Воздуходувки</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>12986897</v>
+        <v>1335169</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>payload</t>
-        </is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
+        <v>31.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>21.2</v>
+        <v>18.3</v>
       </c>
       <c r="P20" t="n">
-        <v>21.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 40 бар» Я10.7</t>
+          <t>«роторная воздуходувка» G18.3; «купить роторную воздуходувку» G5.2; «воздуходувка роторная цена» G10.6</t>
         </is>
       </c>
     </row>
@@ -1767,73 +1793,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>служебная</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-bezmaslyanye</t>
+          <t>https://cmprg.ru/service</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>cmprg.ru</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>8567838</v>
+        <v>808032</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+          <t>прайс-сегмент</t>
+        </is>
       </c>
       <c r="L21" t="n">
-        <v>38.1</v>
+        <v>15.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>22</v>
       </c>
       <c r="O21" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="P21" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>«безмасляный компрессор купить» G15.6; «безмасляный воздушный компрессор» G18.4; «безмасляный воздушный компрессор купить» G14.9</t>
-        </is>
+        <v>17.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>резерв</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/rotornye-vozdukhoduvki</t>
+          <t>https://enger-air.ru/catalog/tsentrobezhnye-kompressory</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1843,7 +1851,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Воздуходувки</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1855,26 +1863,29 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>22.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
-        <v>31.2</v>
-      </c>
       <c r="N22" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O22" t="n">
-        <v>18.3</v>
+        <v>15.9</v>
       </c>
       <c r="P22" t="n">
-        <v>12.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>«роторная воздуходувка» G18.3; «купить роторную воздуходувку» G5.2; «воздуходувка роторная цена» G10.6</t>
+          <t>«центробежные компрессоры» G7.8; «центробежные компрессоры цена» G7.3; «центробежные компрессоры купить» G3.8</t>
         </is>
       </c>
     </row>
@@ -1882,62 +1893,70 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>резерв</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>служебная</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://cmprg.ru/service</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/vintovye_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>cmprg.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>808032</v>
+        <v>8567838</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>10.5</v>
       </c>
       <c r="L23" t="n">
-        <v>15.6</v>
+        <v>10.6</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>17.8</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>17.8</v>
+        <v>14</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>«безмасляный винтовой компрессор» G10.1; «винтовые безмасляные компрессоры купить» G12.6; «безмасляный винтовой компрессор купить» G9.1</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/tsentrobezhnye-kompressory</t>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/membrannie</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1947,41 +1966,41 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Азотные станции</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1335169</v>
+        <v>2451874</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>8.300000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>14.4</v>
+        <v>12.3</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="P24" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>«центробежные компрессоры» G7.8; «центробежные компрессоры цена» G7.3; «центробежные компрессоры купить» G3.8</t>
+          <t>«мембранные генераторы азота» G3.6; «промышленный генератор азота» G9.1; «генераторы азота» G8.8</t>
         </is>
       </c>
     </row>
@@ -1989,14 +2008,9 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/vintovye_1</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vysokogo-davleniya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2006,11 +2020,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Дожимные/ВД</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8567838</v>
+        <v>5896106</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2018,26 +2032,29 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>10.5</v>
+        <v>6.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>35</v>
       </c>
       <c r="L25" t="n">
-        <v>10.6</v>
+        <v>14.8</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O25" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="P25" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>«безмасляный винтовой компрессор» G10.1; «винтовые безмасляные компрессоры купить» G12.6; «безмасляный винтовой компрессор купить» G9.1</t>
+          <t>«компрессор высокого давления» Я13.3; «промышленный компрессор высокого давления» G8.7; «электрический компрессор высокого давления» G3.5</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2069,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/membrannie</t>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota/generator_azota_kolonnogo_tipa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2074,29 +2091,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
+        <v>24.6</v>
       </c>
       <c r="L26" t="n">
         <v>12.3</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>«мембранные генераторы азота» G3.6; «промышленный генератор азота» G9.1; «генераторы азота» G8.8</t>
+          <t>«азотная установка rdrus.ru» Я7.4; «азотная станция принцип работы» G5.5; «азотная установка принцип работы» G11.1</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2120,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vysokogo-davleniya</t>
+          <t>https://prokompressor.ru/services/uslugi/tekhnicheskoe-obsluzhivanie-kompressora</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2116,41 +2130,38 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Дожимные/ВД</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5896106</v>
+        <v>808032</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K27" t="n">
-        <v>35</v>
+        <v>28.5</v>
       </c>
       <c r="L27" t="n">
-        <v>14.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>13.5</v>
       </c>
       <c r="O27" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="P27" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>«компрессор высокого давления» Я13.3; «промышленный компрессор высокого давления» G8.7; «электрический компрессор высокого давления» G3.5</t>
+          <t>«то компрессоров» Я7.8; «обслуживание компрессора воздушного» Я8.9; «обслуживание компрессоров» Я8.7</t>
         </is>
       </c>
     </row>
@@ -2165,17 +2176,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota/generator_azota_kolonnogo_tipa</t>
+          <t>https://prokompressor.ru/catalog/generatsiya-gazov/generatory-kisloroda</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Азотные станции</t>
+          <t>Кислородные станции</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2183,30 +2194,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="L28" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K28" t="n">
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>10.8</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>«азотная установка rdrus.ru» Я7.4; «азотная станция принцип работы» G5.5; «азотная установка принцип работы» G11.1</t>
+          <t>«генератор кислорода промышленный» G15.5; «генератор кислорода для лазерной резки» G4.9</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2224,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/tekhnicheskoe-obsluzhivanie-kompressora</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/dalgakiran</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2238,26 +2246,26 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>28.5</v>
+        <v>6.3</v>
       </c>
       <c r="L29" t="n">
-        <v>8.199999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="O29" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="P29" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>«то компрессоров» Я7.8; «обслуживание компрессора воздушного» Я8.9; «обслуживание компрессоров» Я8.7</t>
+          <t>«далгакиран компрессор» G5.9; «компрессор винтовой далгакиран» G4.7; «поршневые компрессоры dalgakiran» G3.9</t>
         </is>
       </c>
     </row>
@@ -2265,14 +2273,9 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/generatsiya-gazov/generatory-kisloroda</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/atlas-copco</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2282,35 +2285,41 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Кислородные станции</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2451874</v>
+        <v>808032</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>15.6</v>
+        <v>4.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>8</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>13.1</v>
       </c>
       <c r="O30" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="P30" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>«генератор кислорода промышленный» G15.5; «генератор кислорода для лазерной резки» G4.9</t>
+          <t>«винтовой компрессор atlas copco» Я9.7; «компрессор atlas copco» Я10.1; «атлас копко компрессор» G7.8</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2329,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/dalgakiran</t>
+          <t>https://enger-air.ru/catalog/kompressory-nizkogo-davleniya</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2334,34 +2343,37 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>808032</v>
+        <v>1335169</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>13.3</v>
+        <v>5.1</v>
       </c>
       <c r="O31" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="P31" t="n">
-        <v>10.7</v>
+        <v>6.9</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>«далгакиран компрессор» G5.9; «компрессор винтовой далгакиран» G4.7; «поршневые компрессоры dalgakiran» G3.9</t>
+          <t>«компрессор низкого давления» Я12.6; «компрессоры. низкого. давления. воздуходувки.» G4.5; «компрессоры низкого давления» Я9.5</t>
         </is>
       </c>
     </row>
@@ -2369,14 +2381,19 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/atlas-copco</t>
+          <t>https://enger-air.ru/manuals</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2385,91 +2402,79 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>808032</v>
+        <v>1335169</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K32" t="n">
-        <v>21</v>
+          <t>битрикс-бренд</t>
+        </is>
       </c>
       <c r="L32" t="n">
-        <v>11.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>13.1</v>
+        <v>5.1</v>
       </c>
       <c r="O32" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="P32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор atlas copco» Я9.7; «компрессор atlas copco» Я10.1; «атлас копко компрессор» G7.8</t>
-        </is>
+        <v>6.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/kompressory-nizkogo-davleniya</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/porshnevye</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1335169</v>
+        <v>8567838</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M33" t="n">
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="O33" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="P33" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>«компрессор низкого давления» Я12.6; «компрессоры. низкого. давления. воздуходувки.» G4.5; «компрессоры низкого давления» Я9.5</t>
+          <t>«поршневой безмасляный компрессор купить» G6.7; «купить безмасляный поршневой компрессор» G12.7; «поршневой безмасляный компрессор» G6.4</t>
         </is>
       </c>
     </row>
@@ -2479,17 +2484,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>фасет-дубль</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/manuals</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1000-l-min</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2498,41 +2503,47 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1335169</v>
+        <v>808032</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9</v>
       </c>
       <c r="L34" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="O34" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>10.3</v>
-      </c>
       <c r="P34" t="n">
-        <v>6.9</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>«компрессор 1000 л мин» G8.3; «компрессор 1000 л/мин» G4.8; «компрессор 1000 л мин купить» G5.0</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/porshnevye</t>
+          <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-kompressora</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2542,35 +2553,35 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>8567838</v>
+        <v>808032</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>10</v>
+      </c>
+      <c r="M35" t="n">
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="O35" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>«поршневой безмасляный компрессор купить» G6.7; «купить безмасляный поршневой компрессор» G12.7; «поршневой безмасляный компрессор» G6.4</t>
+          <t>«винтовой компрессор ремонт» Я10.0; «винтовой компрессор ремонт promcomtech.ru/remont-vintovykh-kompressorov/» Я10.9; «ремонт винтовых компрессоров» Я8.3</t>
         </is>
       </c>
     </row>
@@ -2580,56 +2591,50 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>фасет-дубль</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1000-l-min</t>
+          <t>https://berg-compressor.com/catalog/vintovye-kompressory</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>berg-compressor.com</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>808032</v>
+        <v>1557410</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>7.8</v>
+        <v>18.8</v>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
-      </c>
-      <c r="L36" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>12.1</v>
+        <v>4.4</v>
       </c>
       <c r="O36" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="P36" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>«компрессор 1000 л мин» G8.3; «компрессор 1000 л/мин» G4.8; «компрессор 1000 л мин купить» G5.0</t>
+          <t>«купить винтовой компрессор» G15.6; «винтовой компрессор купить» G14.6; «винтовые компрессоры официальный сайт» G6.2</t>
         </is>
       </c>
     </row>
@@ -2637,9 +2642,14 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-kompressora</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/elektricheskie_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2653,31 +2663,37 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>808032</v>
+        <v>1523189</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>10.8</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="P37" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>«винтовой компрессор ремонт» Я10.0; «винтовой компрессор ремонт promcomtech.ru/remont-vintovykh-kompressorov/» Я10.9; «ремонт винтовых компрессоров» Я8.3</t>
+          <t>«компрессор винтовой воздушный электрический» G14.0; «компрессоры винтовые электрические» G13.5; «компрессор воздушный винтовой электрический» G10.8</t>
         </is>
       </c>
     </row>
@@ -2685,52 +2701,53 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://berg-compressor.com/catalog/vintovye-kompressory</t>
+          <t>https://prokompressor.ru/catalog</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>berg-compressor.com</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1557410</v>
+        <v>808032</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>18.8</v>
+        <v>21.7</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
       </c>
+      <c r="L38" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="P38" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>«купить винтовой компрессор» G15.6; «винтовой компрессор купить» G14.6; «винтовые компрессоры официальный сайт» G6.2</t>
+          <t>«компрессор центр барнаул» G7.4; «каталог компрессоров» G17.2</t>
         </is>
       </c>
     </row>
@@ -2738,58 +2755,47 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/elektricheskie_1</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-085ha</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1523189</v>
+        <v>1004759</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
+          <t>битрикс-бренд+кат.</t>
+        </is>
       </c>
       <c r="L39" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
         <v>4.9</v>
       </c>
       <c r="O39" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="P39" t="n">
-        <v>7.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>«компрессор винтовой воздушный электрический» G14.0; «компрессоры винтовые электрические» G13.5; «компрессор воздушный винтовой электрический» G10.8</t>
+          <t>«рефрижераторный осушитель» Я11.3; «рефрижераторный осушитель воздуха» Я9.7</t>
         </is>
       </c>
     </row>
@@ -2797,9 +2803,14 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-5000-l-min</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2821,29 +2832,26 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>21.7</v>
+        <v>9.6</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="P40" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>«компрессор центр барнаул» G7.4; «каталог компрессоров» G17.2</t>
+          <t>«компрессор 5000 л мин» G8.4; «винтовой компрессор 5000 л мин» Я9.8; «компрессор 5 м3 мин» G8.6</t>
         </is>
       </c>
     </row>
@@ -2851,9 +2859,14 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-085ha</t>
+          <t>https://enger-air.ru/catalog</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2863,50 +2876,40 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1004759</v>
+        <v>1335169</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="P41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>«рефрижераторный осушитель» Я11.3; «рефрижераторный осушитель воздуха» Я9.7</t>
-        </is>
+        <v>4.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>фасет-дубль</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-5000-l-min</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2928,26 +2931,26 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K42" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M42" t="n">
         <v>4</v>
       </c>
-      <c r="L42" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="N42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="P42" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>«компрессор 5000 л мин» G8.4; «винтовой компрессор 5000 л мин» Я9.8; «компрессор 5 м3 мин» G8.6</t>
+          <t>«компрессор» G14.2; «винтовой компрессор 400 литров в минуту» Я10.1; «компрессорное оборудование купить» Я10.2</t>
         </is>
       </c>
     </row>
@@ -2957,17 +2960,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog</t>
+          <t>https://dali-kompressor.ru/catalog/ca</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>dali-kompressor.ru</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2976,36 +2979,46 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1335169</v>
+        <v>4462526</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>битрикс-бренд</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2</v>
+      <c r="J43" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="O43" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="P43" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>«винтовой компрессор cross air» G8.0; «винтовой компрессор кросс аир» G6.4; «кросс аир компрессор» G6.6</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-500-l-min</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3027,26 +3040,26 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>35.1</v>
+        <v>12.2</v>
       </c>
       <c r="L44" t="n">
-        <v>20.6</v>
+        <v>15.4</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="O44" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="P44" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>«компрессор» G14.2; «винтовой компрессор 400 литров в минуту» Я10.1; «компрессорное оборудование купить» Я10.2</t>
+          <t>«компрессор 500 литров в минуту» G8.6; «компрессор 500л» G11.2; «компрессор 500 л мин цена» G10.7</t>
         </is>
       </c>
     </row>
@@ -3061,45 +3074,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://dali-kompressor.ru/catalog/ca</t>
+          <t>https://ac-kompressor.ru/catalog/dizelnye-kompressory-do-8-bar/dizelnyy-kompressor-atlas-copco-xas-48-kd-</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>dali-kompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>4462526</v>
+        <v>2355138</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K45" t="n">
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M45" t="n">
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="O45" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="P45" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>«винтовой компрессор cross air» G8.0; «винтовой компрессор кросс аир» G6.4; «кросс аир компрессор» G6.6</t>
+          <t>«дизельные компрессоры атлас» Я9.1; «компрессор дизельный атлас копко» Я8.8</t>
         </is>
       </c>
     </row>
@@ -3107,14 +3120,9 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>фасет-дубль</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-500-l-min</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-lazernoy-rezki</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3136,26 +3144,26 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>12.2</v>
+        <v>10.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="M46" t="n">
-        <v>5</v>
+        <v>29.9</v>
       </c>
       <c r="N46" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="P46" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>«компрессор 500 литров в минуту» G8.6; «компрессор 500л» G11.2; «компрессор 500 л мин цена» G10.7</t>
+          <t>«компрессор для лазерной резки металла» G9.5; «винтовой компрессор для лазерного станка» G10.8; «компрессор для лазерного гравера» G8.9</t>
         </is>
       </c>
     </row>
@@ -3163,52 +3171,47 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/dizelnye-kompressory-do-8-bar/dizelnyy-kompressor-atlas-copco-xas-48-kd-</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-300-bar</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2355138</v>
+        <v>774697</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1</v>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="P47" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>«дизельные компрессоры атлас» Я9.1; «компрессор дизельный атлас копко» Я8.8</t>
+          <t>«компрессор высокого давления 300 бар» G8.6; «компрессор высокого давления 300 атм купить» G8.5; «компрессор 300 бар» G7.6</t>
         </is>
       </c>
     </row>
@@ -3216,14 +3219,19 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-lazernoy-rezki</t>
+          <t>https://zif-kompressor.ru/catalog/vzryvozashchishchennye-kompressory</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>zif-kompressor.ru</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3232,34 +3240,31 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>808032</v>
+        <v>3050183</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3</v>
+          <t>битрикс-бренд</t>
+        </is>
       </c>
       <c r="L48" t="n">
-        <v>29.9</v>
+        <v>11.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="O48" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="P48" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>«компрессор для лазерной резки металла» G9.5; «винтовой компрессор для лазерного станка» G10.8; «компрессор для лазерного гравера» G8.9</t>
+          <t>«взрывозащищенные компрессоры» Я8.4</t>
         </is>
       </c>
     </row>
@@ -3267,47 +3272,52 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-300-bar</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-205ha</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>774697</v>
+        <v>1004759</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>payload</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3</v>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>11</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="P49" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>«компрессор высокого давления 300 бар» G8.6; «компрессор высокого давления 300 атм купить» G8.5; «компрессор 300 бар» G7.6</t>
+          <t>«осушитель воздуха с охлаждением» Я7.8</t>
         </is>
       </c>
     </row>
@@ -3315,19 +3325,14 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://zif-kompressor.ru/catalog/vzryvozashchishchennye-kompressory</t>
+          <t>https://abac-kompressor.ru/catalog/spinn-mini</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>zif-kompressor.ru</t>
+          <t>abac-kompressor.ru</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3336,31 +3341,34 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3050183</v>
+        <v>808032</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>34.5</v>
       </c>
       <c r="L50" t="n">
-        <v>11.2</v>
+        <v>7.7</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P50" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>«взрывозащищенные компрессоры» Я8.4</t>
+          <t>«винтовой мини компрессор» Я7.5; «компрессор миниатюрный винтовой» Я7.7</t>
         </is>
       </c>
     </row>
@@ -3368,52 +3376,47 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-205ha</t>
+          <t>https://ac-kompressor.ru/catalog/ga-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1004759</v>
+        <v>808032</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="O51" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P51" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>«осушитель воздуха с охлаждением» Я7.8</t>
+          <t>«компрессор atlas copco ga11ff» Я6.9</t>
         </is>
       </c>
     </row>
@@ -3423,12 +3426,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://abac-kompressor.ru/catalog/spinn-mini</t>
+          <t>https://ac-kompressor.ru/catalog/ga-37</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>abac-kompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3444,11 +3447,8 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="J52" t="n">
-        <v>34.5</v>
-      </c>
       <c r="L52" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M52" t="n">
         <v>4</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>«винтовой мини компрессор» Я7.5; «компрессор миниатюрный винтовой» Я7.7</t>
+          <t>«винтовой компрессор 37 квт» Я6.4</t>
         </is>
       </c>
     </row>
@@ -3472,9 +3472,14 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga-11</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-peredvizhnye</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3484,11 +3489,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>808032</v>
+        <v>2355138</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3496,23 +3501,23 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>8.300000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="O53" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="P53" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>«компрессор atlas copco ga11ff» Я6.9</t>
+          <t>«компрессор дизельный передвижной атлас копко» Я10.6; «дизельные компрессоры atlas copco купить» Я11.6</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3527,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga-37</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/bustery</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3543,24 +3548,30 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6</v>
+      </c>
       <c r="L54" t="n">
-        <v>8.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="M54" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O54" t="n">
         <v>4</v>
       </c>
-      <c r="N54" t="n">
-        <v>6</v>
-      </c>
-      <c r="O54" t="n">
-        <v>4.8</v>
-      </c>
       <c r="P54" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 37 квт» Я6.4</t>
+          <t>«дожимной компрессор» G10.9; «компрессор» Я17.5</t>
         </is>
       </c>
     </row>
@@ -3568,14 +3579,9 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-peredvizhnye</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-ga</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3585,35 +3591,38 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2355138</v>
+        <v>808032</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J55" t="n">
+        <v>32.2</v>
+      </c>
       <c r="L55" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="O55" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>«компрессор дизельный передвижной атлас копко» Я10.6; «дизельные компрессоры atlas copco купить» Я11.6</t>
+          <t>«компрессор atlas copco» Я11.7; «компрессор atlas copco ga» Я8.5; «atlas copco компрессор» Я11.3</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3632,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/bustery</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/rkz</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3644,14 +3653,8 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="J56" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K56" t="n">
-        <v>6</v>
-      </c>
       <c r="L56" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="M56" t="n">
         <v>3</v>
@@ -3667,7 +3670,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>«дожимной компрессор» G10.9; «компрессор» Я17.5</t>
+          <t>«ркз компрессор официальный сайт» Я7.5; «ркз компрессор» Я9.8</t>
         </is>
       </c>
     </row>
@@ -3675,14 +3678,19 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-ga</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1500-l-min</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3699,26 +3707,29 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>32.2</v>
+        <v>15.2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
       </c>
       <c r="L57" t="n">
         <v>10.6</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P57" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>«компрессор atlas copco» Я11.7; «компрессор atlas copco ga» Я8.5; «atlas copco компрессор» Я11.3</t>
+          <t>«компрессор винтовой 1500 л мин» Я10.6; «компрессор 1500 л мин» G13.0; «компрессор 1500 л мин цена» G10.4</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3739,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/rkz</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12-bar</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3749,24 +3760,30 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J58" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
+      </c>
       <c r="L58" t="n">
-        <v>11.3</v>
+        <v>24.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P58" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>«ркз компрессор официальный сайт» Я7.5; «ркз компрессор» Я9.8</t>
+          <t>«компрессор воздушный 12 атмосфер» G8.7; «компрессоры 12 атмосфер» G5.4; «компрессоры 12 квт» G3.8</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3793,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>фасет-дубль</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1500-l-min</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-tsekha</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3803,29 +3820,26 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>15.2</v>
+        <v>18</v>
       </c>
       <c r="K59" t="n">
         <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1</v>
+        <v>34.3</v>
       </c>
       <c r="N59" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O59" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P59" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>«компрессор винтовой 1500 л мин» Я10.6; «компрессор 1500 л мин» G13.0; «компрессор 1500 л мин цена» G10.4</t>
+          <t>«компрессор промышленный» G17.4; «компрессор воздушный промышленный» G17.9; «компрессор промышленный купить» G15.7</t>
         </is>
       </c>
     </row>
@@ -3833,53 +3847,52 @@
       <c r="A60" t="n">
         <v>59</v>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12-bar</t>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/elektricheskie-kompressory</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>808032</v>
+        <v>1335169</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K60" t="n">
-        <v>3</v>
+          <t>битрикс-бренд</t>
+        </is>
       </c>
       <c r="L60" t="n">
-        <v>24.8</v>
+        <v>10.1</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="O60" t="n">
         <v>3.6</v>
       </c>
       <c r="P60" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>«компрессор воздушный 12 атмосфер» G8.7; «компрессоры 12 атмосфер» G5.4; «компрессоры 12 квт» G3.8</t>
+          <t>«цена передвижные компрессоры» Я10.7; «купить передвижные компрессоры» Я10.9</t>
         </is>
       </c>
     </row>
@@ -3887,19 +3900,14 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-tsekha</t>
+          <t>https://ac-kompressor.ru/catalog/ga55</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3915,17 +3923,14 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="J61" t="n">
-        <v>18</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2</v>
-      </c>
       <c r="L61" t="n">
-        <v>34.3</v>
+        <v>9.4</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
         <v>3.6</v>
@@ -3935,7 +3940,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>«компрессор промышленный» G17.4; «компрессор воздушный промышленный» G17.9; «компрессор промышленный купить» G15.7</t>
+          <t>«винтовой компрессор 55 квт» Я6.7</t>
         </is>
       </c>
     </row>
@@ -3943,52 +3948,47 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/elektricheskie-kompressory</t>
+          <t>https://ac-kompressor.ru/catalog/xas</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1335169</v>
+        <v>808032</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>10.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
         <v>3.6</v>
       </c>
       <c r="P62" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>«цена передвижные компрессоры» Я10.7; «купить передвижные компрессоры» Я10.9</t>
+          <t>«дизельный компрессор atlas copco» Я9.8; «дизельные компрессоры xas» Я8.7; «дизельный компрессор atlas» Я8.4</t>
         </is>
       </c>
     </row>
@@ -3998,45 +3998,51 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga55</t>
+          <t>https://prokompressor.ru/catalog/osushiteli</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>808032</v>
+        <v>792758</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K63" t="n">
+        <v>64</v>
       </c>
       <c r="L63" t="n">
-        <v>9.4</v>
+        <v>21.7</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O63" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P63" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 55 квт» Я6.7</t>
+          <t>«осушитель сжатого воздуха для компрессора» G9.6; «осушитель сжатого воздуха» G17.5; «осушитель для компрессора цена» G4.8</t>
         </is>
       </c>
     </row>
@@ -4046,45 +4052,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/xas</t>
+          <t>https://remeza-kompressor.ru/catalog/modulnye-kompressornye-stantsii</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>remeza-kompressor.ru</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Модульные/блочные КС</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>808032</v>
+        <v>741144</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>9.199999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="M64" t="n">
         <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O64" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>«дизельный компрессор atlas copco» Я9.8; «дизельные компрессоры xas» Я8.7; «дизельный компрессор atlas» Я8.4</t>
+          <t>«модульная компрессорная станция» Я10.7</t>
         </is>
       </c>
     </row>
@@ -4092,53 +4098,52 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/osushiteli</t>
+          <t>https://crossair-compressor.ru/catalog/vintovye-kompressory</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>crossair-compressor.ru</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>792758</v>
+        <v>838752</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K65" t="n">
-        <v>64</v>
+          <t>битрикс-бренд</t>
+        </is>
       </c>
       <c r="L65" t="n">
-        <v>21.7</v>
+        <v>11.6</v>
       </c>
       <c r="M65" t="n">
         <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="O65" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P65" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>«осушитель сжатого воздуха для компрессора» G9.6; «осушитель сжатого воздуха» G17.5; «осушитель для компрессора цена» G4.8</t>
+          <t>«винтовой компрессор cross air» Я10.5; «винтовой компрессор кросс аир» Я10.2; «cross air компрессор винтовой» Я10.4</t>
         </is>
       </c>
     </row>
@@ -4146,47 +4151,58 @@
       <c r="A66" t="n">
         <v>65</v>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://remeza-kompressor.ru/catalog/modulnye-kompressornye-stantsii</t>
+          <t>https://prokompressor.ru/catalog/osushiteli/refrizheratornye</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>remeza-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Модульные/блочные КС</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>741144</v>
+        <v>792758</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>15.2</v>
+        <v>26.7</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="O66" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P66" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>«модульная компрессорная станция» Я10.7</t>
+          <t>«рефрижераторный осушитель воздуха» G18.8; «рефрижераторный осушитель сжатого воздуха» G18.8; «осушитель рефрижераторного типа купить» G10.5</t>
         </is>
       </c>
     </row>
@@ -4196,17 +4212,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://crossair-compressor.ru/catalog/vintovye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/5000-to-5000</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>crossair-compressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4215,31 +4231,31 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>838752</v>
+        <v>1523189</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O67" t="n">
         <v>3.4</v>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>«винтовой компрессор cross air» Я10.5; «винтовой компрессор кросс аир» Я10.2; «cross air компрессор винтовой» Я10.4</t>
+          <t>«винтовой компрессор 5000 л мин» Я15.3; «винтовой компрессор 5000 л мин цена» Я8.3</t>
         </is>
       </c>
     </row>
@@ -4249,17 +4265,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/osushiteli/refrizheratornye</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4268,37 +4284,31 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>792758</v>
+        <v>1004759</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
+          <t>битрикс-бренд+кат.</t>
+        </is>
       </c>
       <c r="L68" t="n">
-        <v>26.7</v>
+        <v>20.9</v>
       </c>
       <c r="M68" t="n">
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="O68" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P68" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>«рефрижераторный осушитель воздуха» G18.8; «рефрижераторный осушитель сжатого воздуха» G18.8; «осушитель рефрижераторного типа купить» G10.5</t>
+          <t>«осушители воздуха аирфловер» Я10.6</t>
         </is>
       </c>
     </row>
@@ -4308,50 +4318,50 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>фасет-дубль; кликов 1</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/5000-to-5000</t>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1523189</v>
+        <v>1335169</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="M69" t="n">
         <v>1</v>
       </c>
       <c r="N69" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P69" t="n">
         <v>2.2</v>
       </c>
-      <c r="O69" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P69" t="n">
-        <v>3.4</v>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 5000 л мин» Я15.3; «винтовой компрессор 5000 л мин цена» Я8.3</t>
+          <t>«компрессор воздушный передвижной» Я11.8; «компрессор воздушный дизельный» Я10.6; «компрессор мобильный дизельный» Я11.6</t>
         </is>
       </c>
     </row>
@@ -4359,52 +4369,53 @@
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha</t>
+          <t>https://prokompressor.ru/catalog/resivery</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Ресиверы</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1004759</v>
+        <v>113458</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>12</v>
       </c>
       <c r="L70" t="n">
-        <v>20.9</v>
+        <v>33.4</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
-        <v>2.2</v>
+        <v>28</v>
       </c>
       <c r="O70" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P70" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>«осушители воздуха аирфловер» Я10.6</t>
+          <t>«ресивер для компрессора» G14.7; «воздушный ресивер» G16.0; «купить ресивер для воздуха» G4.2</t>
         </is>
       </c>
     </row>
@@ -4419,45 +4430,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1335169</v>
+        <v>808032</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>10.6</v>
+        <v>18.7</v>
       </c>
       <c r="M71" t="n">
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="O71" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P71" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>«компрессор воздушный передвижной» Я11.8; «компрессор воздушный дизельный» Я10.6; «компрессор мобильный дизельный» Я11.6</t>
+          <t>«компрессоры для производства» Я17.2</t>
         </is>
       </c>
     </row>
@@ -4465,9 +4476,14 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>фасет-дубль; кликов 1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/resivery</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-moshchnosti/11-kvt</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4477,42 +4493,31 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ресиверы</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>113458</v>
+        <v>808032</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K72" t="n">
-        <v>12</v>
+          <t>прайс-сегмент</t>
+        </is>
       </c>
       <c r="L72" t="n">
-        <v>33.4</v>
+        <v>17.1</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>28</v>
+        <v>3.7</v>
       </c>
       <c r="O72" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>«ресивер для компрессора» G14.7; «воздушный ресивер» G16.0; «купить ресивер для воздуха» G4.2</t>
-        </is>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4526,7 +4531,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-peskostruya/soplo-8-mm</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4548,7 +4553,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>18.7</v>
+        <v>16.9</v>
       </c>
       <c r="M73" t="n">
         <v>1</v>
@@ -4564,7 +4569,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>«компрессоры для производства» Я17.2</t>
+          <t>«компрессор для пескоструя» Я16.1; «компрессор винтовой для пескоструя» Я17.6</t>
         </is>
       </c>
     </row>
@@ -4574,17 +4579,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>фасет-дубль; кликов 1</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-moshchnosti/11-kvt</t>
+          <t>https://remeza-kompressor.ru/catalog/kompressory</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>remeza-kompressor.ru</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4593,15 +4598,15 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>808032</v>
+        <v>741144</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
@@ -4610,10 +4615,15 @@
         <v>3.7</v>
       </c>
       <c r="O74" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P74" t="n">
-        <v>3</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>«компрессоры воздушные ремезов» Я12.5</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4627,45 +4637,45 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-peskostruya/soplo-8-mm</t>
+          <t>https://berg-compressor.com/catalog/kompressory-na-resivere</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>berg-compressor.com</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Ресиверы</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>808032</v>
+        <v>449403</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="M75" t="n">
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>«компрессор для пескоструя» Я16.1; «компрессор винтовой для пескоструя» Я17.6</t>
+          <t>«винтовой компрессор на ресивере» G15.4</t>
         </is>
       </c>
     </row>
@@ -4675,17 +4685,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://remeza-kompressor.ru/catalog/kompressory</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-zr</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>remeza-kompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4694,32 +4704,27 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>741144</v>
+        <v>808032</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>17.5</v>
+        <v>12.3</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N76" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="O76" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P76" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>«компрессоры воздушные ремезов» Я12.5</t>
-        </is>
+        <v>2.6</v>
       </c>
     </row>
     <row r="77">
@@ -4728,50 +4733,53 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://berg-compressor.com/catalog/kompressory-na-resivere</t>
+          <t>https://ac-kompressor.ru/catalog/vintovye-kompressory</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>berg-compressor.com</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ресиверы</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>449403</v>
+        <v>808032</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="L77" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
       </c>
       <c r="N77" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="O77" t="n">
         <v>2.6</v>
       </c>
       <c r="P77" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>«винтовой компрессор на ресивере» G15.4</t>
+          <t>«винтовой компрессор atlas copco» Я11.7; «купить винтовой компрессор атлас копко» Я11.3; «винтовой компрессор атлас копко» Я10.6</t>
         </is>
       </c>
     </row>
@@ -4781,46 +4789,51 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-zr</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/adsorbtsionnye_osushiteli/goryachaya_regeneratsiya/kolonnyy_tip_raskhod_vozdukha_na_regeneratsiyu_4_6/ADH-038L</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители адсорбц.</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>808032</v>
+        <v>1004759</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="O78" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P78" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>«адсорбционный осушитель» Я16.5</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4829,17 +4842,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/vintovye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/atlas-copco</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4848,34 +4861,31 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>808032</v>
+        <v>1523189</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>34</v>
+          <t>битрикс-катег.</t>
+        </is>
       </c>
       <c r="L79" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="O79" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>«винтовой компрессор atlas copco» Я11.7; «купить винтовой компрессор атлас копко» Я11.3; «винтовой компрессор атлас копко» Я10.6</t>
+          <t>«винтовой компрессор atlas» Я10.1; «винтовой компрессор atlas copco авито» Я10.5; «купить винтовой компрессор атлас копко» Я10.9</t>
         </is>
       </c>
     </row>
@@ -4885,50 +4895,50 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/adsorbtsionnye_osushiteli/goryachaya_regeneratsiya/kolonnyy_tip_raskhod_vozdukha_na_regeneratsiyu_4_6/ADH-038L</t>
+          <t>https://berg-compressor.com/catalog/refrizheratornye-osushiteli</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>berg-compressor.com</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Осушители адсорбц.</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1004759</v>
+        <v>442250</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>битрикс-бренд+кат.</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1</v>
+      <c r="J80" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
       </c>
       <c r="N80" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="O80" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P80" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>«адсорбционный осушитель» Я16.5</t>
+          <t>«рефрижераторный осушитель» G15.6; «осушитель рефрижераторный» G9.2; «рефрижераторный осушитель воздуха» G11.4</t>
         </is>
       </c>
     </row>
@@ -4943,45 +4953,48 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/atlas-copco</t>
+          <t>https://enger-air.ru/catalog/kompressory-40-bar</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1523189</v>
+        <v>1335169</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N81" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O81" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P81" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>«винтовой компрессор atlas» Я10.1; «винтовой компрессор atlas copco авито» Я10.5; «купить винтовой компрессор атлас копко» Я10.9</t>
+          <t>«винтовой компрессор 40 бар» G11.1; «дожимной компрессор высокого давления» G7.5; «дожимной компрессор 40 бар» G3.9</t>
         </is>
       </c>
     </row>
@@ -4991,50 +5004,50 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://berg-compressor.com/catalog/refrizheratornye-osushiteli</t>
+          <t>https://enger-air.ru/catalog/vintovye_kompressory/lazer</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>berg-compressor.com</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>442250</v>
+        <v>1335169</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>13.7</v>
+        <v>7.9</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="O82" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P82" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>«рефрижераторный осушитель» G15.6; «осушитель рефрижераторный» G9.2; «рефрижераторный осушитель воздуха» G11.4</t>
+          <t>«винтовой компрессор для лазерной резки» G5.2</t>
         </is>
       </c>
     </row>
@@ -5044,17 +5057,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/kompressory-40-bar</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12000-l-min</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5063,34 +5076,34 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1335169</v>
+        <v>808032</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K83" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L83" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M83" t="n">
         <v>1</v>
       </c>
-      <c r="L83" t="n">
-        <v>14</v>
-      </c>
       <c r="N83" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="O83" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P83" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 40 бар» G11.1; «дожимной компрессор высокого давления» G7.5; «дожимной компрессор 40 бар» G3.9</t>
+          <t>«компрессор 12000 л/мин» G5.2; «компрессоры 12000 л/мин» G3.7; «компрессор 75 квт» G11.1</t>
         </is>
       </c>
     </row>
@@ -5105,12 +5118,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/vintovye_kompressory/lazer</t>
+          <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-bloka</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5119,31 +5132,34 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1335169</v>
+        <v>808032</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K84" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L84" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M84" t="n">
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="O84" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P84" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>«винтовой компрессор для лазерной резки» G5.2</t>
+          <t>«ремонт винтового компрессора» G11.1; «ремонт винтового блока компрессора» Я9.0; «ремонт винтовых блоков» Я10.1</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5174,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12000-l-min</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15000-l-min</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5180,26 +5196,26 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O85" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="P85" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>«компрессор 12000 л/мин» G5.2; «компрессоры 12000 л/мин» G3.7; «компрессор 75 квт» G11.1</t>
+          <t>«компрессор 15 бар» G10.3; «винтовой компрессор 15 м3 мин» Я7.9; «купить компрессор 15 атмосфер» G9.6</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5230,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-bloka</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-20-bar</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5224,7 +5240,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5236,26 +5252,26 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>8.9</v>
+        <v>10.9</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1</v>
+        <v>18.3</v>
       </c>
       <c r="N86" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O86" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="P86" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>«ремонт винтового компрессора» G11.1; «ремонт винтового блока компрессора» Я9.0; «ремонт винтовых блоков» Я10.1</t>
+          <t>«компрессор 20 бар» G11.9; «компрессор 20 бар цена» G8.5; «купить компрессор 20 атмосфер» G8.2</t>
         </is>
       </c>
     </row>
@@ -5265,12 +5281,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>фасет-дубль; кликов 1</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15000-l-min</t>
+          <t>https://prokompressor.ru/catalog/osushiteli/adsorbtsionnye</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5280,38 +5296,41 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители адсорбц.</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>808032</v>
+        <v>792758</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>11.2</v>
+        <v>17.3</v>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>8.800000000000001</v>
+        <v>32.4</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O87" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P87" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>«компрессор 15 бар» G10.3; «винтовой компрессор 15 м3 мин» Я7.9; «купить компрессор 15 атмосфер» G9.6</t>
+          <t>«адсорбционный осушитель» G12.3; «адсорбционный осушитель воздуха» G19.7; «адсорбционный осушитель воздуха купить» G15.6</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5345,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-20-bar</t>
+          <t>https://prokompressor.ru/services/uslugi/montazh</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5347,28 +5366,20 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="J88" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M88" t="n">
         <v>1</v>
       </c>
-      <c r="L88" t="n">
-        <v>18.3</v>
-      </c>
       <c r="N88" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O88" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="P88" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>«компрессор 20 бар» G11.9; «компрессор 20 бар цена» G8.5; «купить компрессор 20 атмосфер» G8.2</t>
-        </is>
+        <v>1.8</v>
       </c>
     </row>
     <row r="89">
@@ -5377,12 +5388,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/osushiteli/adsorbtsionnye</t>
+          <t>https://prokompressor.ru/services/uslugi/remont-osushiteley</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5392,31 +5403,25 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Осушители адсорбц.</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>792758</v>
+        <v>493116</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
+          <t>прайс-сегмент</t>
+        </is>
       </c>
       <c r="L89" t="n">
-        <v>32.4</v>
+        <v>15.6</v>
       </c>
       <c r="M89" t="n">
         <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="O89" t="n">
         <v>1.8</v>
@@ -5426,7 +5431,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>«адсорбционный осушитель» G12.3; «адсорбционный осушитель воздуха» G19.7; «адсорбционный осушитель воздуха купить» G15.6</t>
+          <t>«ремонт осушителя воздуха для компрессора» Я14.9</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5446,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/montazh</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/cross-air</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5462,20 +5467,28 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J90" t="n">
+        <v>13.4</v>
+      </c>
       <c r="L90" t="n">
-        <v>21.3</v>
+        <v>15.4</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="O90" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="P90" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>«винтовой компрессор cross air» G14.8; «компрессор cross air» G13.6</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5484,12 +5497,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>служебная; кликов 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/remont-osushiteley</t>
+          <t>https://prokompressor.ru/services/uslugi</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5499,11 +5512,11 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>493116</v>
+        <v>808032</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5511,23 +5524,23 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="M91" t="n">
         <v>1</v>
       </c>
       <c r="N91" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="O91" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="P91" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>«ремонт осушителя воздуха для компрессора» Я14.9</t>
+          <t>«обслуживание компрессора» Я10.2; «компрессор тех центр serviceset» Я4.2; «установка и обслуживание компрессоров» Я5.9</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5555,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/cross-air</t>
+          <t>https://prokompressor.ru/projects/proizvodstvo/cross-air-argus</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5563,27 +5576,24 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="J92" t="n">
-        <v>13.4</v>
-      </c>
       <c r="L92" t="n">
-        <v>15.4</v>
+        <v>9.1</v>
       </c>
       <c r="M92" t="n">
         <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O92" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P92" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>«винтовой компрессор cross air» G14.8; «компрессор cross air» G13.6</t>
+          <t>«аргус компрессор» Я10.9</t>
         </is>
       </c>
     </row>
@@ -5593,17 +5603,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>служебная; кликов 1</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-gx</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5620,23 +5630,23 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O93" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="P93" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>«обслуживание компрессора» Я10.2; «компрессор тех центр serviceset» Я4.2; «установка и обслуживание компрессоров» Я5.9</t>
+          <t>«atlas copco компрессор» Я10.7; «компрессор atlas copco gx11ff» Я10.8</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5656,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>служебная; кликов 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/projects/proizvodstvo/cross-air-argus</t>
+          <t>https://ac-kompressor.ru/company/service</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5673,23 +5683,23 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>9.1</v>
+        <v>11.5</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O94" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="P94" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>«аргус компрессор» Я10.9</t>
+          <t>«компрессор атлас копко обслуживание» Я7.9</t>
         </is>
       </c>
     </row>
@@ -5704,12 +5714,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-gx</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15-bar</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5725,24 +5735,27 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J95" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
       <c r="L95" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1</v>
+        <v>26.6</v>
       </c>
       <c r="N95" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O95" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="P95" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>«atlas copco компрессор» Я10.7; «компрессор atlas copco gx11ff» Я10.8</t>
+          <t>«компрессор 15 бар» G7.6; «винтовой компрессор 15 бар» G8.2; «компрессор воздушный 15 бар» G8.0</t>
         </is>
       </c>
     </row>
@@ -5752,17 +5765,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>служебная; кликов 1</t>
+          <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/company/service</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-3000-l-min</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5778,131 +5791,22 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="L96" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M96" t="n">
+      <c r="J96" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K96" t="n">
         <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O96" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="P96" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q96" t="inlineStr">
-        <is>
-          <t>«компрессор атлас копко обслуживание» Я7.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15-bar</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="N97" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>«компрессор 15 бар» G7.6; «винтовой компрессор 15 бар» G8.2; «компрессор воздушный 15 бар» G8.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>фасет-дубль; кликов 1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-3000-l-min</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N98" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q98" t="inlineStr">
         <is>
           <t>«компрессор 3000 л мин» G7.2; «компрессор 3000 литров в минуту» G6.3; «винтовой компрессор 3000 л мин» G6.8</t>
         </is>

--- a/seo-texts/frog/acceptor-top100.xlsx
+++ b/seo-texts/frog/acceptor-top100.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1165,63 +1165,52 @@
           <t>ЯДРО</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>служебная</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services</t>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Азотные станции</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>808032</v>
+        <v>2451874</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>не проверить</t>
+          <t>ок</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>28.2</v>
+        <v>11.4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M11" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>58.5</v>
+        <v>11.7</v>
       </c>
       <c r="O11" t="n">
-        <v>47.2</v>
+        <v>42.9</v>
       </c>
       <c r="P11" t="n">
-        <v>47.2</v>
+        <v>28.6</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>«ремонт и обслуживание компрессоров» G10.9; «техническое обслуживание компрессоров теплообменников» Я5.0; «обслуживание винтовых компрессоров» G16.0</t>
+          <t>«генератор азота цена» G18.2; «генератор азота» G14.1; «адсорбционный генератор азота» G7.6</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1241,25 +1230,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Азотные станции</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2451874</v>
+        <v>1523189</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1268,23 +1257,29 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11.4</v>
+        <v>17.9</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
       </c>
       <c r="N12" t="n">
-        <v>11.7</v>
+        <v>25.9</v>
       </c>
       <c r="O12" t="n">
-        <v>42.9</v>
+        <v>39.5</v>
       </c>
       <c r="P12" t="n">
-        <v>28.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>«генератор азота цена» G18.2; «генератор азота» G14.1; «адсорбционный генератор азота» G7.6</t>
+          <t>«винтовой компрессор» G15.0; «стоимость винтового компрессора» G10.7; «компрессор промышленный винтовой» G15.7</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1304,56 +1299,56 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1523189</v>
+        <v>1004759</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ок</t>
+          <t>завышен</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17.9</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>15.4</v>
+        <v>23.8</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>25.9</v>
+        <v>24.4</v>
       </c>
       <c r="O13" t="n">
-        <v>39.5</v>
+        <v>36.7</v>
       </c>
       <c r="P13" t="n">
-        <v>39.5</v>
+        <v>24.5</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>«винтовой компрессор» G15.0; «стоимость винтового компрессора» G10.7; «компрессор промышленный винтовой» G15.7</t>
+          <t>«рефрижераторный осушитель воздуха» G6.4; «осушитель рефрижераторного типа» G5.8; «осушитель сжатого воздуха рефрижераторного типа» G5.5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1373,7 +1368,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli</t>
+          <t>https://enger-air.ru/catalog/mks</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1383,51 +1378,41 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1004759</v>
+        <v>1335169</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>завышен</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>23.8</v>
+        <v>10.5</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>24.4</v>
+        <v>15.9</v>
       </c>
       <c r="O14" t="n">
-        <v>36.7</v>
+        <v>31.8</v>
       </c>
       <c r="P14" t="n">
-        <v>24.5</v>
+        <v>21.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>«рефрижераторный осушитель воздуха» G6.4; «осушитель рефрижераторного типа» G5.8; «осушитель сжатого воздуха рефрижераторного типа» G5.5</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>агент: качать</t>
+          <t>«модульные компрессорные станции» G6.4; «модульная компрессорная станция мкс» G8.3; «компрессорная» G8.3</t>
         </is>
       </c>
     </row>
@@ -1442,51 +1427,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/mks</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/dizelnye</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1335169</v>
+        <v>2355138</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>10.5</v>
+        <v>22.1</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>15.9</v>
+        <v>10.1</v>
       </c>
       <c r="O15" t="n">
-        <v>31.8</v>
+        <v>23.8</v>
       </c>
       <c r="P15" t="n">
-        <v>21.2</v>
+        <v>23.8</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>«модульные компрессорные станции» G6.4; «модульная компрессорная станция мкс» G8.3; «компрессорная» G8.3</t>
+          <t>«дизельный компрессор» G10.5; «компрессоры винтовые дизельные воздушные» G7.7; «винтовой компрессор на шасси» G11.8</t>
         </is>
       </c>
     </row>
@@ -1501,51 +1486,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/dizelnye</t>
+          <t>https://enger-air.ru/catalog/kislorodnye-ustanovki/generator-kisloroda</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Кислородные станции</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2355138</v>
+        <v>2451874</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>10.1</v>
+        <v>6.3</v>
       </c>
       <c r="O16" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.8</v>
+        <v>15.5</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>«дизельный компрессор» G10.5; «компрессоры винтовые дизельные воздушные» G7.7; «винтовой компрессор на шасси» G11.8</t>
+          <t>«генератор кислорода» G10.4; «кислородный генератор» G10.9; «кислородные генераторы» G14.7</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1537,52 @@
           <t>ЯДРО</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/kislorodnye-ustanovki/generator-kisloroda</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/kompressory-40-bar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Кислородные станции</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2451874</v>
+        <v>12986897</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>23.2</v>
+        <v>21.2</v>
       </c>
       <c r="P17" t="n">
-        <v>15.5</v>
+        <v>21.2</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>«генератор кислорода» G10.4; «кислородный генератор» G10.9; «кислородные генераторы» G14.7</t>
+          <t>«винтовой компрессор 40 бар» Я10.7</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1592,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ЯДРО</t>
+          <t>резерв</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1618,7 +1602,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/kompressory-40-bar</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-bezmaslyanye</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1628,35 +1612,38 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>12986897</v>
+        <v>8567838</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>payload</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
+        <v>38.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>21.2</v>
+        <v>18.4</v>
       </c>
       <c r="P18" t="n">
-        <v>21.2</v>
+        <v>18.4</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 40 бар» Я10.7</t>
+          <t>«безмасляный компрессор купить» G15.6; «безмасляный воздушный компрессор» G18.4; «безмасляный воздушный компрессор купить» G14.9</t>
         </is>
       </c>
     </row>
@@ -1671,53 +1658,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-bezmaslyanye</t>
+          <t>https://enger-air.ru/catalog/rotornye-vozdukhoduvki</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Воздуходувки</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>8567838</v>
+        <v>1335169</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13.6</v>
+        <v>22.9</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>38.1</v>
+        <v>31.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P19" t="n">
-        <v>18.4</v>
+        <v>12.2</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>«безмасляный компрессор купить» G15.6; «безмасляный воздушный компрессор» G18.4; «безмасляный воздушный компрессор купить» G14.9</t>
+          <t>«роторная воздуходувка» G18.3; «купить роторную воздуходувку» G5.2; «воздуходувка роторная цена» G10.6</t>
         </is>
       </c>
     </row>
@@ -1725,19 +1712,9 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>резерв</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/rotornye-vozdukhoduvki</t>
+          <t>https://enger-air.ru/catalog/tsentrobezhnye-kompressory</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1747,7 +1724,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Воздуходувки</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1759,26 +1736,29 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>22.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M20" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
-        <v>31.2</v>
-      </c>
       <c r="N20" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>18.3</v>
+        <v>15.9</v>
       </c>
       <c r="P20" t="n">
-        <v>12.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>«роторная воздуходувка» G18.3; «купить роторную воздуходувку» G5.2; «воздуходувка роторная цена» G10.6</t>
+          <t>«центробежные компрессоры» G7.8; «центробежные компрессоры цена» G7.3; «центробежные компрессоры купить» G3.8</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1766,70 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>резерв</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>служебная</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://cmprg.ru/service</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/vintovye_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>cmprg.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>808032</v>
+        <v>8567838</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>10.5</v>
       </c>
       <c r="L21" t="n">
-        <v>15.6</v>
+        <v>10.6</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>22</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>17.8</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
-        <v>17.8</v>
+        <v>14</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>«безмасляный винтовой компрессор» G10.1; «винтовые безмасляные компрессоры купить» G12.6; «безмасляный винтовой компрессор купить» G9.1</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/tsentrobezhnye-kompressory</t>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/membrannie</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1851,41 +1839,41 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Азотные станции</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1335169</v>
+        <v>2451874</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>8.300000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>14.4</v>
+        <v>12.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="P22" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>«центробежные компрессоры» G7.8; «центробежные компрессоры цена» G7.3; «центробежные компрессоры купить» G3.8</t>
+          <t>«мембранные генераторы азота» G3.6; «промышленный генератор азота» G9.1; «генераторы азота» G8.8</t>
         </is>
       </c>
     </row>
@@ -1893,14 +1881,9 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/vintovye_1</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vysokogo-davleniya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1910,11 +1893,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Дожимные/ВД</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8567838</v>
+        <v>5896106</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1922,26 +1905,29 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10.5</v>
+        <v>6.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>35</v>
       </c>
       <c r="L23" t="n">
-        <v>10.6</v>
+        <v>14.8</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>«безмасляный винтовой компрессор» G10.1; «винтовые безмасляные компрессоры купить» G12.6; «безмасляный винтовой компрессор купить» G9.1</t>
+          <t>«компрессор высокого давления» Я13.3; «промышленный компрессор высокого давления» G8.7; «электрический компрессор высокого давления» G3.5</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1942,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/membrannie</t>
+          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota/generator_azota_kolonnogo_tipa</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1978,29 +1964,26 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
+        <v>24.6</v>
       </c>
       <c r="L24" t="n">
         <v>12.3</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>«мембранные генераторы азота» G3.6; «промышленный генератор азота» G9.1; «генераторы азота» G8.8</t>
+          <t>«азотная установка rdrus.ru» Я7.4; «азотная станция принцип работы» G5.5; «азотная установка принцип работы» G11.1</t>
         </is>
       </c>
     </row>
@@ -2008,9 +1991,14 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vysokogo-davleniya</t>
+          <t>https://prokompressor.ru/catalog/generatsiya-gazov/generatory-kisloroda</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2020,11 +2008,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Дожимные/ВД</t>
+          <t>Кислородные станции</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5896106</v>
+        <v>2451874</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2032,29 +2020,23 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6.7</v>
+        <v>15.6</v>
       </c>
       <c r="K25" t="n">
-        <v>35</v>
-      </c>
-      <c r="L25" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
-        <v>13.1</v>
+        <v>10.8</v>
       </c>
       <c r="P25" t="n">
-        <v>13.1</v>
+        <v>10.8</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>«компрессор высокого давления» Я13.3; «промышленный компрессор высокого давления» G8.7; «электрический компрессор высокого давления» G3.5</t>
+          <t>«генератор кислорода промышленный» G15.5; «генератор кислорода для лазерной резки» G4.9</t>
         </is>
       </c>
     </row>
@@ -2062,55 +2044,50 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/azotnye-ustanovki/generatory_azota/generator_azota_kolonnogo_tipa</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/dalgakiran</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Азотные станции</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2451874</v>
+        <v>808032</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>24.6</v>
+        <v>6.3</v>
       </c>
       <c r="L26" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="O26" t="n">
-        <v>12</v>
+        <v>10.7</v>
       </c>
       <c r="P26" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>«азотная установка rdrus.ru» Я7.4; «азотная станция принцип работы» G5.5; «азотная установка принцип работы» G11.1</t>
+          <t>«далгакиран компрессор» G5.9; «компрессор винтовой далгакиран» G4.7; «поршневые компрессоры dalgakiran» G3.9</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2097,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/tekhnicheskoe-obsluzhivanie-kompressora</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/atlas-copco</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2142,26 +2119,29 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>28.5</v>
+        <v>4.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>8.199999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="M27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="O27" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="P27" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>«то компрессоров» Я7.8; «обслуживание компрессора воздушного» Я8.9; «обслуживание компрессоров» Я8.7</t>
+          <t>«винтовой компрессор atlas copco» Я9.7; «компрессор atlas copco» Я10.1; «атлас копко компрессор» G7.8</t>
         </is>
       </c>
     </row>
@@ -2169,52 +2149,53 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/generatsiya-gazov/generatory-kisloroda</t>
+          <t>https://enger-air.ru/catalog/kompressory-nizkogo-davleniya</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Кислородные станции</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2451874</v>
+        <v>1335169</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>15.6</v>
+        <v>7.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="P28" t="n">
-        <v>10.8</v>
+        <v>6.9</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>«генератор кислорода промышленный» G15.5; «генератор кислорода для лазерной резки» G4.9</t>
+          <t>«компрессор низкого давления» Я12.6; «компрессоры. низкого. давления. воздуходувки.» G4.5; «компрессоры низкого давления» Я9.5</t>
         </is>
       </c>
     </row>
@@ -2222,9 +2203,14 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/dalgakiran</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/porshnevye</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2234,38 +2220,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Безмасляные/центробежные</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>808032</v>
+        <v>8567838</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6</v>
+        <v>9.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>13.3</v>
+        <v>1.2</v>
       </c>
       <c r="O29" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="P29" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>«далгакиран компрессор» G5.9; «компрессор винтовой далгакиран» G4.7; «поршневые компрессоры dalgakiran» G3.9</t>
+          <t>«поршневой безмасляный компрессор купить» G6.7; «купить безмасляный поршневой компрессор» G12.7; «поршневой безмасляный компрессор» G6.4</t>
         </is>
       </c>
     </row>
@@ -2273,9 +2256,14 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>фасет-дубль</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/atlas-copco</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1000-l-min</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2297,29 +2285,29 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L30" t="n">
         <v>11.9</v>
       </c>
       <c r="M30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="O30" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>«винтовой компрессор atlas copco» Я9.7; «компрессор atlas copco» Я10.1; «атлас копко компрессор» G7.8</t>
+          <t>«компрессор 1000 л мин» G8.3; «компрессор 1000 л/мин» G4.8; «компрессор 1000 л мин купить» G5.0</t>
         </is>
       </c>
     </row>
@@ -2327,53 +2315,52 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/kompressory-nizkogo-davleniya</t>
+          <t>https://berg-compressor.com/catalog/vintovye-kompressory</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>berg-compressor.com</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1335169</v>
+        <v>1557410</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>7.6</v>
+        <v>18.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="P31" t="n">
         <v>6.9</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>«компрессор низкого давления» Я12.6; «компрессоры. низкого. давления. воздуходувки.» G4.5; «компрессоры низкого давления» Я9.5</t>
+          <t>«купить винтовой компрессор» G15.6; «винтовой компрессор купить» G14.6; «винтовые компрессоры официальный сайт» G6.2</t>
         </is>
       </c>
     </row>
@@ -2388,93 +2375,99 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/manuals</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/elektricheskie_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1335169</v>
+        <v>1523189</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O32" t="n">
-        <v>10.3</v>
+        <v>7.5</v>
       </c>
       <c r="P32" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>«компрессор винтовой воздушный электрический» G14.0; «компрессоры винтовые электрические» G13.5; «компрессор воздушный винтовой электрический» G10.8</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu-smazki/bezmaslyanye_1/porshnevye</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-085ha</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Безмасляные/центробежные</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8567838</v>
+        <v>1004759</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="O33" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="P33" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>«поршневой безмасляный компрессор купить» G6.7; «купить безмасляный поршневой компрессор» G12.7; «поршневой безмасляный компрессор» G6.4</t>
+          <t>«рефрижераторный осушитель» Я11.3; «рефрижераторный осушитель воздуха» Я9.7</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2482,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1000-l-min</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-5000-l-min</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2511,29 +2504,26 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N34" t="n">
         <v>9</v>
       </c>
-      <c r="L34" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>12.1</v>
-      </c>
       <c r="O34" t="n">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="P34" t="n">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>«компрессор 1000 л мин» G8.3; «компрессор 1000 л/мин» G4.8; «компрессор 1000 л мин купить» G5.0</t>
+          <t>«компрессор 5000 л мин» G8.4; «винтовой компрессор 5000 л мин» Я9.8; «компрессор 5 м3 мин» G8.6</t>
         </is>
       </c>
     </row>
@@ -2541,47 +2531,52 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-kompressora</t>
+          <t>https://dali-kompressor.ru/catalog/ca</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>dali-kompressor.ru</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>808032</v>
+        <v>4462526</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>10</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6</v>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="O35" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="P35" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>«винтовой компрессор ремонт» Я10.0; «винтовой компрессор ремонт promcomtech.ru/remont-vintovykh-kompressorov/» Я10.9; «ремонт винтовых компрессоров» Я8.3</t>
+          <t>«винтовой компрессор cross air» G8.0; «винтовой компрессор кросс аир» G6.4; «кросс аир компрессор» G6.6</t>
         </is>
       </c>
     </row>
@@ -2591,50 +2586,53 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>фасет-дубль</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://berg-compressor.com/catalog/vintovye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-500-l-min</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>berg-compressor.com</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1557410</v>
+        <v>808032</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
+        <v>12.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>4.4</v>
+        <v>7.9</v>
       </c>
       <c r="O36" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="P36" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>«купить винтовой компрессор» G15.6; «винтовой компрессор купить» G14.6; «винтовые компрессоры официальный сайт» G6.2</t>
+          <t>«компрессор 500 литров в минуту» G8.6; «компрессор 500л» G11.2; «компрессор 500 л мин цена» G10.7</t>
         </is>
       </c>
     </row>
@@ -2644,56 +2642,50 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/elektricheskie_1</t>
+          <t>https://ac-kompressor.ru/catalog/dizelnye-kompressory-do-8-bar/dizelnyy-kompressor-atlas-copco-xas-48-kd-</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1523189</v>
+        <v>2355138</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
+          <t>прайс-сегмент</t>
+        </is>
       </c>
       <c r="L37" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="P37" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>«компрессор винтовой воздушный электрический» G14.0; «компрессоры винтовые электрические» G13.5; «компрессор воздушный винтовой электрический» G10.8</t>
+          <t>«дизельные компрессоры атлас» Я9.1; «компрессор дизельный атлас копко» Я8.8</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2695,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-lazernoy-rezki</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2725,29 +2717,26 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>21.7</v>
+        <v>10.8</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5</v>
+        <v>29.9</v>
       </c>
       <c r="N38" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="P38" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>«компрессор центр барнаул» G7.4; «каталог компрессоров» G17.2</t>
+          <t>«компрессор для лазерной резки металла» G9.5; «винтовой компрессор для лазерного станка» G10.8; «компрессор для лазерного гравера» G8.9</t>
         </is>
       </c>
     </row>
@@ -2757,45 +2746,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-085ha</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-300-bar</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1004759</v>
+        <v>774697</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M39" t="n">
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K39" t="n">
         <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="P39" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>«рефрижераторный осушитель» Я11.3; «рефрижераторный осушитель воздуха» Я9.7</t>
+          <t>«компрессор высокого давления 300 бар» G8.6; «компрессор высокого давления 300 атм купить» G8.5; «компрессор 300 бар» G7.6</t>
         </is>
       </c>
     </row>
@@ -2805,17 +2794,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>фасет-дубль</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-5000-l-min</t>
+          <t>https://zif-kompressor.ru/catalog/vzryvozashchishchennye-kompressory</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>zif-kompressor.ru</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2824,34 +2813,31 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>808032</v>
+        <v>3050183</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4</v>
+          <t>битрикс-бренд</t>
+        </is>
       </c>
       <c r="L40" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="O40" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="P40" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>«компрессор 5000 л мин» G8.4; «винтовой компрессор 5000 л мин» Я9.8; «компрессор 5 м3 мин» G8.6</t>
+          <t>«взрывозащищенные компрессоры» Я8.4</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2852,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-205ha</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2876,31 +2862,36 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1335169</v>
+        <v>1004759</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="M41" t="n">
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="P41" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>«осушитель воздуха с охлаждением» Я7.8</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2909,12 +2900,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory</t>
+          <t>https://abac-kompressor.ru/catalog/spinn-mini</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>abac-kompressor.ru</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2931,26 +2922,26 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>35.1</v>
+        <v>34.5</v>
       </c>
       <c r="L42" t="n">
-        <v>20.6</v>
+        <v>7.7</v>
       </c>
       <c r="M42" t="n">
         <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="P42" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>«компрессор» G14.2; «винтовой компрессор 400 литров в минуту» Я10.1; «компрессорное оборудование купить» Я10.2</t>
+          <t>«винтовой мини компрессор» Я7.5; «компрессор миниатюрный винтовой» Я7.7</t>
         </is>
       </c>
     </row>
@@ -2958,19 +2949,14 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://dali-kompressor.ru/catalog/ca</t>
+          <t>https://ac-kompressor.ru/catalog/ga-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>dali-kompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2979,31 +2965,31 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4462526</v>
+        <v>808032</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="O43" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="P43" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>«винтовой компрессор cross air» G8.0; «винтовой компрессор кросс аир» G6.4; «кросс аир компрессор» G6.6</t>
+          <t>«компрессор atlas copco ga11ff» Я6.9</t>
         </is>
       </c>
     </row>
@@ -3011,19 +2997,14 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>фасет-дубль</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-500-l-min</t>
+          <t>https://ac-kompressor.ru/catalog/ga-37</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3039,27 +3020,24 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>12.2</v>
-      </c>
       <c r="L44" t="n">
-        <v>15.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="O44" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="P44" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>«компрессор 500 литров в минуту» G8.6; «компрессор 500л» G11.2; «компрессор 500 л мин цена» G10.7</t>
+          <t>«винтовой компрессор 37 квт» Я6.4</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3052,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/dizelnye-kompressory-do-8-bar/dizelnyy-kompressor-atlas-copco-xas-48-kd-</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-peredvizhnye</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3096,23 +3074,23 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="O45" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="P45" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>«дизельные компрессоры атлас» Я9.1; «компрессор дизельный атлас копко» Я8.8</t>
+          <t>«компрессор дизельный передвижной атлас копко» Я10.6; «дизельные компрессоры atlas copco купить» Я11.6</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3100,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-lazernoy-rezki</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/bustery</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3144,26 +3122,29 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>10.8</v>
+        <v>6.4</v>
       </c>
       <c r="K46" t="n">
+        <v>6</v>
+      </c>
+      <c r="L46" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M46" t="n">
         <v>3</v>
       </c>
-      <c r="L46" t="n">
-        <v>29.9</v>
-      </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="O46" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>«компрессор для лазерной резки металла» G9.5; «винтовой компрессор для лазерного станка» G10.8; «компрессор для лазерного гравера» G8.9</t>
+          <t>«дожимной компрессор» G10.9; «компрессор» Я17.5</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3154,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-300-bar</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-ga</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3187,31 +3168,34 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>774697</v>
+        <v>808032</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K47" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M47" t="n">
         <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="O47" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>«компрессор высокого давления 300 бар» G8.6; «компрессор высокого давления 300 атм купить» G8.5; «компрессор 300 бар» G7.6</t>
+          <t>«компрессор atlas copco» Я11.7; «компрессор atlas copco ga» Я8.5; «atlas copco компрессор» Я11.3</t>
         </is>
       </c>
     </row>
@@ -3219,19 +3203,14 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://zif-kompressor.ru/catalog/vzryvozashchishchennye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/rkz</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>zif-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3240,31 +3219,31 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3050183</v>
+        <v>808032</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="O48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>«взрывозащищенные компрессоры» Я8.4</t>
+          <t>«ркз компрессор официальный сайт» Я7.5; «ркз компрессор» Я9.8</t>
         </is>
       </c>
     </row>
@@ -3274,50 +3253,56 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>фасет-дубль</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/refrizheratornye_osushiteli/vozdushnoe_okhlazhdenie/rd-205ha</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1500-l-min</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1004759</v>
+        <v>808032</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="P49" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>«осушитель воздуха с охлаждением» Я7.8</t>
+          <t>«компрессор винтовой 1500 л мин» Я10.6; «компрессор 1500 л мин» G13.0; «компрессор 1500 л мин цена» G10.4</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3312,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://abac-kompressor.ru/catalog/spinn-mini</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12-bar</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>abac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3349,26 +3334,29 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>34.5</v>
+        <v>6.3</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>7.7</v>
+        <v>24.8</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="O50" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P50" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>«винтовой мини компрессор» Я7.5; «компрессор миниатюрный винтовой» Я7.7</t>
+          <t>«компрессор воздушный 12 атмосфер» G8.7; «компрессоры 12 атмосфер» G5.4; «компрессоры 12 квт» G3.8</t>
         </is>
       </c>
     </row>
@@ -3376,14 +3364,19 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga-11</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-tsekha</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3399,24 +3392,27 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J51" t="n">
+        <v>18</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2</v>
+      </c>
       <c r="L51" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4</v>
+        <v>34.3</v>
       </c>
       <c r="N51" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="O51" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P51" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>«компрессор atlas copco ga11ff» Я6.9</t>
+          <t>«компрессор промышленный» G17.4; «компрессор воздушный промышленный» G17.9; «компрессор промышленный купить» G15.7</t>
         </is>
       </c>
     </row>
@@ -3424,47 +3420,52 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga-37</t>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/elektricheskie-kompressory</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>808032</v>
+        <v>1335169</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>8.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="O52" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P52" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 37 квт» Я6.4</t>
+          <t>«цена передвижные компрессоры» Я10.7; «купить передвижные компрессоры» Я10.9</t>
         </is>
       </c>
     </row>
@@ -3472,14 +3473,9 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-peredvizhnye</t>
+          <t>https://ac-kompressor.ru/catalog/ga55</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3489,11 +3485,11 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2355138</v>
+        <v>808032</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3501,23 +3497,23 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="O53" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P53" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>«компрессор дизельный передвижной атлас копко» Я10.6; «дизельные компрессоры atlas copco купить» Я11.6</t>
+          <t>«винтовой компрессор 55 квт» Я6.7</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3523,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/bustery</t>
+          <t>https://ac-kompressor.ru/catalog/xas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3548,30 +3544,24 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
-      <c r="J54" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K54" t="n">
-        <v>6</v>
-      </c>
       <c r="L54" t="n">
-        <v>12.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M54" t="n">
         <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>«дожимной компрессор» G10.9; «компрессор» Я17.5</t>
+          <t>«дизельный компрессор atlas copco» Я9.8; «дизельные компрессоры xas» Я8.7; «дизельный компрессор atlas» Я8.4</t>
         </is>
       </c>
     </row>
@@ -3581,48 +3571,51 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-ga</t>
+          <t>https://prokompressor.ru/catalog/osushiteli</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>808032</v>
+        <v>792758</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>32.2</v>
+        <v>7.4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>64</v>
       </c>
       <c r="L55" t="n">
-        <v>10.6</v>
+        <v>21.7</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P55" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>«компрессор atlas copco» Я11.7; «компрессор atlas copco ga» Я8.5; «atlas copco компрессор» Я11.3</t>
+          <t>«осушитель сжатого воздуха для компрессора» G9.6; «осушитель сжатого воздуха» G17.5; «осушитель для компрессора цена» G4.8</t>
         </is>
       </c>
     </row>
@@ -3632,45 +3625,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/rkz</t>
+          <t>https://remeza-kompressor.ru/catalog/modulnye-kompressornye-stantsii</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>remeza-kompressor.ru</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Модульные/блочные КС</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>808032</v>
+        <v>741144</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>11.3</v>
+        <v>15.2</v>
       </c>
       <c r="M56" t="n">
         <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P56" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>«ркз компрессор официальный сайт» Я7.5; «ркз компрессор» Я9.8</t>
+          <t>«модульная компрессорная станция» Я10.7</t>
         </is>
       </c>
     </row>
@@ -3680,56 +3673,50 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>фасет-дубль</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-1500-l-min</t>
+          <t>https://crossair-compressor.ru/catalog/vintovye-kompressory</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>crossair-compressor.ru</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>808032</v>
+        <v>838752</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="K57" t="n">
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M57" t="n">
         <v>2</v>
       </c>
-      <c r="L57" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="O57" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P57" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>«компрессор винтовой 1500 л мин» Я10.6; «компрессор 1500 л мин» G13.0; «компрессор 1500 л мин цена» G10.4</t>
+          <t>«винтовой компрессор cross air» Я10.5; «винтовой компрессор кросс аир» Я10.2; «cross air компрессор винтовой» Я10.4</t>
         </is>
       </c>
     </row>
@@ -3737,9 +3724,14 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12-bar</t>
+          <t>https://prokompressor.ru/catalog/osushiteli/refrizheratornye</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3749,41 +3741,41 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>808032</v>
+        <v>792758</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>6.3</v>
+        <v>14.5</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>24.8</v>
+        <v>26.7</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O58" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P58" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>«компрессор воздушный 12 атмосфер» G8.7; «компрессоры 12 атмосфер» G5.4; «компрессоры 12 квт» G3.8</t>
+          <t>«рефрижераторный осушитель воздуха» G18.8; «рефрижераторный осушитель сжатого воздуха» G18.8; «осушитель рефрижераторного типа купить» G10.5</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3785,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-tsekha</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/5000-to-5000</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3808,38 +3800,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>808032</v>
+        <v>1523189</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>18</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2</v>
+          <t>битрикс-катег.</t>
+        </is>
       </c>
       <c r="L59" t="n">
-        <v>34.3</v>
+        <v>13.6</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="O59" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P59" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>«компрессор промышленный» G17.4; «компрессор воздушный промышленный» G17.9; «компрессор промышленный купить» G15.7</t>
+          <t>«винтовой компрессор 5000 л мин» Я15.3; «винтовой компрессор 5000 л мин цена» Я8.3</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3843,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory/elektricheskie-kompressory</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3864,35 +3853,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Осушители</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1335169</v>
+        <v>1004759</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="M60" t="n">
         <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O60" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P60" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>«цена передвижные компрессоры» Я10.7; «купить передвижные компрессоры» Я10.9</t>
+          <t>«осушители воздуха аирфловер» Я10.6</t>
         </is>
       </c>
     </row>
@@ -3900,47 +3889,52 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/ga55</t>
+          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Дизельные/передвижные</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>808032</v>
+        <v>1335169</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>прайс-сегмент</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="O61" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 55 квт» Я6.7</t>
+          <t>«компрессор воздушный передвижной» Я11.8; «компрессор воздушный дизельный» Я10.6; «компрессор мобильный дизельный» Я11.6</t>
         </is>
       </c>
     </row>
@@ -3948,14 +3942,19 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>фасет-дубль; кликов 1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/xas</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-moshchnosti/11-kvt</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3972,33 +3971,33 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>9.199999999999999</v>
+        <v>17.1</v>
       </c>
       <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="N62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P62" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>«дизельный компрессор atlas copco» Я9.8; «дизельные компрессоры xas» Я8.7; «дизельный компрессор atlas» Я8.4</t>
-        </is>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>62</v>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/osushiteli</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-peskostruya/soplo-8-mm</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4008,41 +4007,35 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>792758</v>
+        <v>808032</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K63" t="n">
-        <v>64</v>
+          <t>прайс-сегмент</t>
+        </is>
       </c>
       <c r="L63" t="n">
-        <v>21.7</v>
+        <v>16.9</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="O63" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P63" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>«осушитель сжатого воздуха для компрессора» G9.6; «осушитель сжатого воздуха» G17.5; «осушитель для компрессора цена» G4.8</t>
+          <t>«компрессор для пескоструя» Я16.1; «компрессор винтовой для пескоструя» Я17.6</t>
         </is>
       </c>
     </row>
@@ -4050,9 +4043,14 @@
       <c r="A64" t="n">
         <v>63</v>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://remeza-kompressor.ru/catalog/modulnye-kompressornye-stantsii</t>
+          <t>https://remeza-kompressor.ru/catalog/kompressory</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4062,7 +4060,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Модульные/блочные КС</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -4074,23 +4072,23 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>15.2</v>
+        <v>17.5</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="O64" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="P64" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>«модульная компрессорная станция» Я10.7</t>
+          <t>«компрессоры воздушные ремезов» Я12.5</t>
         </is>
       </c>
     </row>
@@ -4105,29 +4103,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://crossair-compressor.ru/catalog/vintovye-kompressory</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-zr</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>crossair-compressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>838752</v>
+        <v>808032</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="M65" t="n">
         <v>2</v>
@@ -4136,15 +4134,10 @@
         <v>3.3</v>
       </c>
       <c r="O65" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="P65" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор cross air» Я10.5; «винтовой компрессор кросс аир» Я10.2; «cross air компрессор винтовой» Я10.4</t>
-        </is>
+        <v>2.6</v>
       </c>
     </row>
     <row r="66">
@@ -4158,51 +4151,48 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/osushiteli/refrizheratornye</t>
+          <t>https://ac-kompressor.ru/catalog/vintovye-kompressory</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>ac-kompressor.ru</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>792758</v>
+        <v>808032</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="L66" t="n">
-        <v>26.7</v>
+        <v>11.3</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O66" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="P66" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>«рефрижераторный осушитель воздуха» G18.8; «рефрижераторный осушитель сжатого воздуха» G18.8; «осушитель рефрижераторного типа купить» G10.5</t>
+          <t>«винтовой компрессор atlas copco» Я11.7; «купить винтовой компрессор атлас копко» Я11.3; «винтовой компрессор атлас копко» Я10.6</t>
         </is>
       </c>
     </row>
@@ -4212,50 +4202,50 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>фасет-дубль; кликов 1</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/5000-to-5000</t>
+          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/adsorbtsionnye_osushiteli/goryachaya_regeneratsiya/kolonnyy_tip_raskhod_vozdukha_na_regeneratsiyu_4_6/ADH-038L</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Осушители адсорбц.</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1523189</v>
+        <v>1004759</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>битрикс-бренд+кат.</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="M67" t="n">
         <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="O67" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P67" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>«винтовой компрессор 5000 л мин» Я15.3; «винтовой компрессор 5000 л мин цена» Я8.3</t>
+          <t>«адсорбционный осушитель» Я16.5</t>
         </is>
       </c>
     </row>
@@ -4270,45 +4260,45 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/atlas-copco</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Осушители</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1004759</v>
+        <v>1523189</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
+          <t>битрикс-катег.</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>20.9</v>
+        <v>11.6</v>
       </c>
       <c r="M68" t="n">
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="O68" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="P68" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>«осушители воздуха аирфловер» Я10.6</t>
+          <t>«винтовой компрессор atlas» Я10.1; «винтовой компрессор atlas copco авито» Я10.5; «купить винтовой компрессор атлас копко» Я10.9</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4313,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/peredvizhnye-kompressory</t>
+          <t>https://enger-air.ru/catalog/kompressory-40-bar</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4333,7 +4323,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Дизельные/передвижные</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4344,24 +4334,27 @@
           <t>битрикс-бренд</t>
         </is>
       </c>
+      <c r="J69" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
       <c r="L69" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N69" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O69" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="P69" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>«компрессор воздушный передвижной» Я11.8; «компрессор воздушный дизельный» Я10.6; «компрессор мобильный дизельный» Я11.6</t>
+          <t>«винтовой компрессор 40 бар» G11.1; «дожимной компрессор высокого давления» G7.5; «дожимной компрессор 40 бар» G3.9</t>
         </is>
       </c>
     </row>
@@ -4369,53 +4362,52 @@
       <c r="A70" t="n">
         <v>69</v>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/resivery</t>
+          <t>https://enger-air.ru/catalog/vintovye_kompressory/lazer</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>prokompressor.ru</t>
+          <t>enger-air.ru</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ресиверы</t>
+          <t>Винтовые</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>113458</v>
+        <v>1335169</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>битрикс-катег.</t>
+          <t>битрикс-бренд</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>12.5</v>
+        <v>7.9</v>
       </c>
       <c r="K70" t="n">
-        <v>12</v>
-      </c>
-      <c r="L70" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="M70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>28</v>
+        <v>1.2</v>
       </c>
       <c r="O70" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="P70" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>«ресивер для компрессора» G14.7; «воздушный ресивер» G16.0; «купить ресивер для воздуха» G4.2</t>
+          <t>«винтовой компрессор для лазерной резки» G5.2</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4417,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12000-l-min</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4451,24 +4443,27 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J71" t="n">
+        <v>15.2</v>
+      </c>
       <c r="L71" t="n">
-        <v>18.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M71" t="n">
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="O71" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="P71" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>«компрессоры для производства» Я17.2</t>
+          <t>«компрессор 12000 л/мин» G5.2; «компрессоры 12000 л/мин» G3.7; «компрессор 75 квт» G11.1</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4478,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-moshchnosti/11-kvt</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15000-l-min</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4504,20 +4499,28 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J72" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
       <c r="L72" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>«компрессор 15 бар» G10.3; «винтовой компрессор 15 м3 мин» Я7.9; «купить компрессор 15 атмосфер» G9.6</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4531,7 +4534,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-naznacheniyu/dlya-peskostruya/soplo-8-mm</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-20-bar</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4552,24 +4555,27 @@
           <t>прайс-сегмент</t>
         </is>
       </c>
+      <c r="J73" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
       <c r="L73" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="M73" t="n">
-        <v>1</v>
+        <v>18.3</v>
       </c>
       <c r="N73" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="P73" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>«компрессор для пескоструя» Я16.1; «компрессор винтовой для пескоструя» Я17.6</t>
+          <t>«компрессор 20 бар» G11.9; «компрессор 20 бар цена» G8.5; «купить компрессор 20 атмосфер» G8.2</t>
         </is>
       </c>
     </row>
@@ -4579,50 +4585,56 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>кликов 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://remeza-kompressor.ru/catalog/kompressory</t>
+          <t>https://prokompressor.ru/catalog/osushiteli/adsorbtsionnye</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>remeza-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Бренд/категория (смеш.)</t>
+          <t>Осушители адсорбц.</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>741144</v>
+        <v>792758</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
-        </is>
+          <t>битрикс-катег.</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>17.5</v>
+        <v>32.4</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="O74" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="P74" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>«компрессоры воздушные ремезов» Я12.5</t>
+          <t>«адсорбционный осушитель» G12.3; «адсорбционный осушитель воздуха» G19.7; «адсорбционный осушитель воздуха купить» G15.6</t>
         </is>
       </c>
     </row>
@@ -4637,45 +4649,48 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://berg-compressor.com/catalog/kompressory-na-resivere</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/cross-air</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>berg-compressor.com</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ресиверы</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>449403</v>
+        <v>808032</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>битрикс-бренд</t>
+          <t>прайс-сегмент</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="K75" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M75" t="n">
         <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="O75" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="P75" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>«винтовой компрессор на ресивере» G15.4</t>
+          <t>«винтовой компрессор cross air» G14.8; «компрессор cross air» G13.6</t>
         </is>
       </c>
     </row>
@@ -4685,12 +4700,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-zr</t>
+          <t>https://ac-kompressor.ru/catalog/kompressory-gx</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4712,19 +4727,24 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>12.3</v>
+        <v>10.9</v>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="O76" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="P76" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>«atlas copco компрессор» Я10.7; «компрессор atlas copco gx11ff» Я10.8</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -4733,22 +4753,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>кликов 2</t>
+          <t>кликов 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://ac-kompressor.ru/catalog/vintovye-kompressory</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15-bar</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ac-kompressor.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Винтовые</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4760,26 +4780,26 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>34</v>
+        <v>7.6</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M77" t="n">
-        <v>2</v>
+        <v>26.6</v>
       </c>
       <c r="N77" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="O77" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="P77" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>«винтовой компрессор atlas copco» Я11.7; «купить винтовой компрессор атлас копко» Я11.3; «винтовой компрессор атлас копко» Я10.6</t>
+          <t>«компрессор 15 бар» G7.6; «винтовой компрессор 15 бар» G8.2; «компрессор воздушный 15 бар» G8.0</t>
         </is>
       </c>
     </row>
@@ -4789,1024 +4809,48 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>кликов 1</t>
+          <t>фасет-дубль; кликов 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://enger-air.ru/catalog/osushiteli_vozdukha/adsorbtsionnye_osushiteli/goryachaya_regeneratsiya/kolonnyy_tip_raskhod_vozdukha_na_regeneratsiyu_4_6/ADH-038L</t>
+          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-3000-l-min</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>enger-air.ru</t>
+          <t>prokompressor.ru</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Осушители адсорбц.</t>
+          <t>Бренд/категория (смеш.)</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1004759</v>
+        <v>808032</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M78" t="n">
+          <t>прайс-сегмент</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O78" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="P78" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q78" t="inlineStr">
-        <is>
-          <t>«адсорбционный осушитель» Я16.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/po-tipu/vintovye/atlas-copco</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Винтовые</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>1523189</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор atlas» Я10.1; «винтовой компрессор atlas copco авито» Я10.5; «купить винтовой компрессор атлас копко» Я10.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>https://berg-compressor.com/catalog/refrizheratornye-osushiteli</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>berg-compressor.com</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Осушители</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>442250</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>битрикс-бренд+кат.</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="K80" t="n">
-        <v>2</v>
-      </c>
-      <c r="N80" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O80" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>«рефрижераторный осушитель» G15.6; «осушитель рефрижераторный» G9.2; «рефрижераторный осушитель воздуха» G11.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/kompressory-40-bar</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>1335169</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>14</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O81" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор 40 бар» G11.1; «дожимной компрессор высокого давления» G7.5; «дожимной компрессор 40 бар» G3.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>https://enger-air.ru/catalog/vintovye_kompressory/lazer</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>enger-air.ru</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Винтовые</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>1335169</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>битрикс-бренд</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O82" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор для лазерной резки» G5.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>фасет-дубль; кликов 1</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-12000-l-min</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="L83" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="N83" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O83" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P83" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>«компрессор 12000 л/мин» G5.2; «компрессоры 12000 л/мин» G3.7; «компрессор 75 квт» G11.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/services/uslugi/remont-vintovogo-bloka</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Винтовые</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L84" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O84" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P84" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>«ремонт винтового компрессора» G11.1; «ремонт винтового блока компрессора» Я9.0; «ремонт винтовых блоков» Я10.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>фасет-дубль; кликов 1</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15000-l-min</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N85" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P85" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>«компрессор 15 бар» G10.3; «винтовой компрессор 15 м3 мин» Я7.9; «купить компрессор 15 атмосфер» G9.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-20-bar</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="N86" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>«компрессор 20 бар» G11.9; «компрессор 20 бар цена» G8.5; «купить компрессор 20 атмосфер» G8.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>кликов 2</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/osushiteli/adsorbtsionnye</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Осушители адсорбц.</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>792758</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>битрикс-катег.</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>«адсорбционный осушитель» G12.3; «адсорбционный осушитель воздуха» G19.7; «адсорбционный осушитель воздуха купить» G15.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/services/uslugi/montazh</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L88" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O88" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P88" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/services/uslugi/remont-osushiteley</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Осушители</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>493116</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P89" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>«ремонт осушителя воздуха для компрессора» Я14.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/cross-air</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="L90" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P90" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>«винтовой компрессор cross air» G14.8; «компрессор cross air» G13.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>служебная; кликов 1</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/services/uslugi</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>«обслуживание компрессора» Я10.2; «компрессор тех центр serviceset» Я4.2; «установка и обслуживание компрессоров» Я5.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/projects/proizvodstvo/cross-air-argus</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="M92" t="n">
-        <v>1</v>
-      </c>
-      <c r="N92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P92" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>«аргус компрессор» Я10.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>https://ac-kompressor.ru/catalog/kompressory-gx</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ac-kompressor.ru</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L93" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M93" t="n">
-        <v>1</v>
-      </c>
-      <c r="N93" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>«atlas copco компрессор» Я10.7; «компрессор atlas copco gx11ff» Я10.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>служебная; кликов 1</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://ac-kompressor.ru/company/service</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ac-kompressor.ru</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="L94" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M94" t="n">
-        <v>1</v>
-      </c>
-      <c r="N94" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>«компрессор атлас копко обслуживание» Я7.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>кликов 1</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-15-bar</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="N95" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>«компрессор 15 бар» G7.6; «винтовой компрессор 15 бар» G8.2; «компрессор воздушный 15 бар» G8.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>фасет-дубль; кликов 1</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://prokompressor.ru/catalog/vozdushnye-kompressory/kompressory-3000-l-min</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>prokompressor.ru</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Бренд/категория (смеш.)</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>808032</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>прайс-сегмент</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q96" t="inlineStr">
         <is>
           <t>«компрессор 3000 л мин» G7.2; «компрессор 3000 литров в минуту» G6.3; «винтовой компрессор 3000 л мин» G6.8</t>
         </is>

--- a/seo-texts/frog/acceptor-top100.xlsx
+++ b/seo-texts/frog/acceptor-top100.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R78"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4856,6 +4856,112 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>кликов 1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://berg-compressor.com/catalog/kompressory-na-resivere</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>berg-compressor.com</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ресиверы</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>449403</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>битрикс-бренд</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O79" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>«винтовой компрессор на ресивере» G15.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>кликов 2</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://berg-compressor.com/catalog/refrizheratornye-osushiteli</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>berg-compressor.com</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Осушители</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>442250</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>битрикс-бренд+кат.</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>«рефрижераторный осушитель» G15.6; «осушитель рефрижераторный» G9.2; «рефрижераторный осушитель воздуха» G11.4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
